--- a/words.xlsx
+++ b/words.xlsx
@@ -437,13 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1355"/>
+  <dimension ref="A1:E1355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>Category</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -513,6 +519,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>La abeja hace miel.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -527,6 +538,11 @@
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>El grifo estaba abierto y el agua caía sin parar.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -541,6 +557,11 @@
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>El abogado defiende a su cliente en el juicio.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -559,6 +580,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Me pongo el abrigo cuando hace mucho frío.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -577,6 +603,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>En abril caen muchas lluvias de primavera.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -623,6 +654,11 @@
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No me gusta esta película en absoluto.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -641,6 +677,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>La madre de mi madre es mi abuela.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -659,6 +700,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>El padre de mi padre es mi abuelo.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -691,6 +737,11 @@
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Necesito acabar este informe antes del viernes.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -705,6 +756,11 @@
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Llevo un paraguas por si acaso llueve.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -719,6 +775,11 @@
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hubo un accidente de coche en la autopista.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -733,6 +794,11 @@
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Me gustan las películas de acción con muchas explosiones.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -747,6 +813,11 @@
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Voy a aceptar tu oferta de trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -775,6 +846,11 @@
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Vamos a acordar un precio justo para los dos.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -807,6 +883,11 @@
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Firmamos un acuerdo de paz entre los dos países.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -835,6 +916,11 @@
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>A pesar de las dificultades, decidió seguir adelante.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -895,6 +981,11 @@
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>¿Adónde vamos de vacaciones este año?</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -913,6 +1004,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Facturo la maleta y espero mi vuelo en el aeropuerto.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -959,6 +1055,11 @@
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>El agente de policía dirige el tráfico en la calle.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -977,6 +1078,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Agosto es el mes de más calor del verano.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1045,6 +1151,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>El agua del mar es salada.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1105,6 +1216,11 @@
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Abro la ventana para que entre aire fresco.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1119,6 +1235,11 @@
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Quiero alegrar tu día con esta sorpresa.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1137,6 +1258,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>La alfombra cubre el suelo del salón.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1235,6 +1361,11 @@
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Dicen que los ojos son el espejo del alma.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1253,6 +1384,11 @@
           <t>dailyverbs</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Salimos a almorzar juntos a mediodía.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1281,6 +1417,11 @@
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Mi hermano es muy alto, mide casi dos metros.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1331,6 +1472,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>El plátano maduro es de color amarillo.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1363,6 +1509,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>La ambulancia lleva a los heridos al hospital.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1377,6 +1528,11 @@
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>La chica con la que voy de compras los sábados es mi amiga.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1391,6 +1547,11 @@
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>El chico con el que voy al gimnasio los sábados es mi amigo.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1405,6 +1566,11 @@
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>El amor de una madre por su hijo es incondicional.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1433,6 +1599,11 @@
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Le doy un anillo de compromiso antes de casarnos.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1461,6 +1632,11 @@
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Anoche no pude dormir porque hacía mucho calor.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1521,6 +1697,11 @@
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Vivo en un apartamento pequeño en el centro de la ciudad.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1549,6 +1730,11 @@
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Mis padres me dan mucho apoyo en mis estudios.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -1631,6 +1817,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>La araña tiene ocho patas y teje una telaraña.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -1649,6 +1840,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Después de la lluvia, a veces aparece un arcoíris de colores.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -1663,6 +1859,11 @@
       </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>El soldado lleva un arma para defenderse en la guerra.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -1681,6 +1882,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Cuelgo la ropa dentro del armario.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -1731,6 +1937,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>En Asia, el arroz es la base de casi todas las comidas.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -1745,6 +1956,11 @@
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>El museo tiene obras de arte muy famosas.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -1759,6 +1975,11 @@
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>La policía busca al asesino que mató a la víctima.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1773,6 +1994,11 @@
       </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Me siento en mi asiento antes de que despegue el avión.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -1833,6 +2059,11 @@
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>El país sufrió un ataque sorpresa durante la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -1847,6 +2078,11 @@
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Presto mucha atención en clase para aprender bien.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -1921,6 +2157,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Espero en la parada al autobús para ir al trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -1939,6 +2180,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Conduzco muy rápido por la autopista.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1971,6 +2217,11 @@
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Quiero averiguar la verdad sobre lo que pasó.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -1989,6 +2240,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>El avión despega y vuela muy alto en el cielo.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2003,6 +2259,11 @@
       </c>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Ayer llovió todo el día sin parar.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2017,6 +2278,11 @@
       </c>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Necesito tu ayuda para terminar este proyecto.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2053,6 +2319,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>El cielo sin nubes es azul.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2071,6 +2342,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Pongo azúcar en el café para que esté más dulce.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2103,6 +2379,11 @@
       </c>
       <c r="C107" s="2" t="inlineStr"/>
       <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Enero es el primer mes del año.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2149,6 +2430,11 @@
       </c>
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aprendemos un baile nuevo en la clase los martes.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2181,6 +2467,11 @@
       </c>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Mi hermano es muy bajo, mide metro y medio.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2195,6 +2486,11 @@
       </c>
       <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>La bala atravesó la pared del edificio.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2213,6 +2509,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>La ballena es el animal más grande del océano.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2227,6 +2528,11 @@
       </c>
       <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Voy al banco para sacar dinero.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2241,6 +2547,11 @@
       </c>
       <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>La banda toca música en vivo en el concierto.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2255,6 +2566,11 @@
       </c>
       <c r="C117" s="2" t="inlineStr"/>
       <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Quedamos en el bar para tomar una cerveza.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2273,6 +2589,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Me apoyo la barbilla en la mano mientras pienso.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2291,6 +2612,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>El capitán guía el barco por el mar.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2347,6 +2673,11 @@
       </c>
       <c r="C123" s="2" t="inlineStr"/>
       <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Tiro la basura todos los días en el contenedor.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -2361,6 +2692,11 @@
       </c>
       <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>El ejército ganó la batalla contra el enemigo.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -2397,6 +2733,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Me ducho y me lavo los dientes en el baño.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -2415,6 +2756,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Me gusta beber agua fría cuando hace calor.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -2433,6 +2779,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>El bebé llora porque tiene hambre.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -2451,6 +2802,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>El beige es un color neutro parecido al color de la arena.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -2465,6 +2821,11 @@
       </c>
       <c r="C130" s="2" t="inlineStr"/>
       <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Su belleza natural no necesita maquillaje.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -2479,6 +2840,11 @@
       </c>
       <c r="C131" s="2" t="inlineStr"/>
       <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Le doy un beso de buenas noches a mi hijo.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -2497,6 +2863,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Pedaleo la bicicleta para hacer ejercicio.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -2547,6 +2918,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Compro un billete antes de subir al tren.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -2565,6 +2941,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>La nieve es de color blanco.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -2583,6 +2964,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Como con la boca cerrada.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -2597,6 +2983,11 @@
       </c>
       <c r="C138" s="2" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Nos invitaron a la boda de mi prima el sábado.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -2611,6 +3002,11 @@
       </c>
       <c r="C139" s="2" t="inlineStr"/>
       <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Meto las compras en una bolsa de plástico.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -2625,6 +3021,11 @@
       </c>
       <c r="C140" s="2" t="inlineStr"/>
       <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>La bomba explotó y destruyó el edificio.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -2653,6 +3054,11 @@
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Los animales viven libres en el bosque.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -2671,6 +3077,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Me pongo las botas para caminar en la nieve.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -2685,6 +3096,11 @@
       </c>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Compro una botella de agua en la tienda.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -2703,6 +3119,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Me rompí el brazo jugando baloncesto.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -2731,6 +3152,11 @@
       </c>
       <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Le hice una broma a mi amigo el día de los inocentes.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -2745,6 +3171,11 @@
       </c>
       <c r="C148" s="2" t="inlineStr"/>
       <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Le gusta bromear con sus compañeros de trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -2867,6 +3298,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>La bufanda me abriga el cuello en invierno.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -2899,6 +3335,11 @@
       </c>
       <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>El caballero luchaba con espada y armadura en la Edad Media.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -2917,6 +3358,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Monto a caballo por el campo.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -2949,6 +3395,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Llevo el sombrero en la cabeza.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -2995,6 +3446,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Bailo moviendo las caderas.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -3031,6 +3487,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Bebo una taza de café por la mañana para despertarme.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -3045,6 +3506,11 @@
       </c>
       <c r="C166" s="2" t="inlineStr"/>
       <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Guardo mis fotos antiguas en una caja de cartón.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -3063,6 +3529,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Me pongo los calcetines antes de los zapatos.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -3077,6 +3548,11 @@
       </c>
       <c r="C168" s="2" t="inlineStr"/>
       <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>El café está muy caliente, ten cuidado al beberlo.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -3091,6 +3567,11 @@
       </c>
       <c r="C169" s="2" t="inlineStr"/>
       <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Prefiero callar antes que decir algo que lastime.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -3123,6 +3604,11 @@
       </c>
       <c r="C171" s="2" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Cruzo la calle cuando el semáforo está en verde.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -3137,6 +3623,11 @@
       </c>
       <c r="C172" s="2" t="inlineStr"/>
       <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Respira con calma antes de hablar en público.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -3151,6 +3642,11 @@
       </c>
       <c r="C173" s="2" t="inlineStr"/>
       <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Intento calmar al bebé que no para de llorar.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -3165,6 +3661,11 @@
       </c>
       <c r="C174" s="2" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Bebo agua fría porque tengo mucho calor.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -3183,6 +3684,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Hago la cama cada mañana al levantarme.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -3215,6 +3721,11 @@
       </c>
       <c r="C177" s="2" t="inlineStr"/>
       <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Me devuelven el cambio después de pagar en la tienda.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -3233,6 +3744,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Me gusta caminar por el parque los domingos.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -3247,6 +3763,11 @@
       </c>
       <c r="C179" s="2" t="inlineStr"/>
       <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Sigo el camino que lleva hasta la montaña.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -3265,6 +3786,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Me pongo una camisa y una corbata para ir a la oficina.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -3283,6 +3809,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Juego al fútbol con la camiseta de mi equipo.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -3301,6 +3832,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>El camión transporta cajas pesadas de una ciudad a otra.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -3315,6 +3851,11 @@
       </c>
       <c r="C183" s="2" t="inlineStr"/>
       <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Los agricultores trabajan la tierra en el campo.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -3329,6 +3870,11 @@
       </c>
       <c r="C184" s="2" t="inlineStr"/>
       <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Escucho mi canción favorita en la radio.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -3393,6 +3939,11 @@
       </c>
       <c r="C188" s="2" t="inlineStr"/>
       <c r="D188" s="2" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Ella es capaz de resolver cualquier problema.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -3407,6 +3958,11 @@
       </c>
       <c r="C189" s="2" t="inlineStr"/>
       <c r="D189" s="2" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>El capitán da órdenes a toda la tripulación del barco.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -3425,6 +3981,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Me lavo la cara por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -3467,6 +4028,11 @@
       </c>
       <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Mi abuela me trata siempre con mucho cariño.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -3485,6 +4051,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Los vegetarianos no comen carne.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -3499,6 +4070,11 @@
       </c>
       <c r="C195" s="2" t="inlineStr"/>
       <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Estudio una carrera de cinco años en la universidad.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -3517,6 +4093,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Conduzco por la carretera que lleva al pueblo.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -3531,6 +4112,11 @@
       </c>
       <c r="C197" s="2" t="inlineStr"/>
       <c r="D197" s="2" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Envío una carta por correo a mi abuela.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -3549,6 +4135,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Después del trabajo, vuelvo a casa.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -3563,6 +4154,11 @@
       </c>
       <c r="C199" s="2" t="inlineStr"/>
       <c r="D199" s="2" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Mi hermano está casado desde hace cinco años.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -3659,6 +4255,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Lloro cuando corto una cebolla.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -3677,6 +4278,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Se pinta las cejas cada mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -3695,6 +4301,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>La bandera de Argentina es blanca y celeste.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -3727,6 +4338,11 @@
       </c>
       <c r="C209" s="2" t="inlineStr"/>
       <c r="D209" s="2" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Preparo la cena para toda la familia esta noche.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -3745,6 +4361,11 @@
           <t>dailyverbs</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Nos gusta cenar juntos por la noche en familia.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -3759,6 +4380,11 @@
       </c>
       <c r="C211" s="2" t="inlineStr"/>
       <c r="D211" s="2" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Vamos de compras al centro de la ciudad.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -3791,6 +4417,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>El cerdo se revuelca en el barro.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -3809,6 +4440,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Pensamos con el cerebro.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -3845,6 +4481,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Pedimos una cerveza bien fría en el bar.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -3881,6 +4522,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Llevo una chaqueta de cuero.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -3895,6 +4541,11 @@
       </c>
       <c r="C219" s="2" t="inlineStr"/>
       <c r="D219" s="2" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>La chica que vive al lado tiene quince años.</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -3909,6 +4560,11 @@
       </c>
       <c r="C220" s="2" t="inlineStr"/>
       <c r="D220" s="2" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>El chico que vive al lado tiene quince años.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -3923,6 +4579,11 @@
       </c>
       <c r="C221" s="2" t="inlineStr"/>
       <c r="D221" s="2" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>No hay ni una nube en el cielo hoy.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -4167,6 +4828,11 @@
       </c>
       <c r="C235" s="2" t="inlineStr"/>
       <c r="D235" s="2" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Vamos al cine a ver una película esta noche.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -4185,6 +4851,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>El cinturón rodea la cintura.</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -4203,6 +4874,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Me pongo el cinturón para sujetar los pantalones.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -4217,6 +4893,11 @@
       </c>
       <c r="C238" s="2" t="inlineStr"/>
       <c r="D238" s="2" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Tengo una cita con el médico mañana por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -4231,6 +4912,11 @@
       </c>
       <c r="C239" s="2" t="inlineStr"/>
       <c r="D239" s="2" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Madrid es la capital de España y una ciudad muy grande.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -4259,6 +4945,11 @@
       </c>
       <c r="C241" s="2" t="inlineStr"/>
       <c r="D241" s="2" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Llego tarde a clase porque perdí el autobús.</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -4273,6 +4964,11 @@
       </c>
       <c r="C242" s="2" t="inlineStr"/>
       <c r="D242" s="2" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>El camarero atiende al cliente en el restaurante.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -4291,6 +4987,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>El clima de esta región es muy seco durante todo el año.</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -4305,6 +5006,11 @@
       </c>
       <c r="C244" s="2" t="inlineStr"/>
       <c r="D244" s="2" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Somos socios de un club de tenis.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -4323,6 +5029,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Conduzco el coche para ir al trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -4341,6 +5052,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Preparo la comida en la cocina.</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -4359,6 +5075,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>A mi madre le encanta cocinar platos españoles.</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -4377,6 +5098,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Golpeo la puerta con el codo porque tengo las manos ocupadas.</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -4447,6 +5173,11 @@
       </c>
       <c r="C253" s="2" t="inlineStr"/>
       <c r="D253" s="2" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>El comandante dirige a sus soldados en la batalla.</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -4465,6 +5196,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Ponemos la mesa grande en el comedor para las visitas.</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -4483,6 +5219,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Los niños tienen hambre y quieren comer.</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -4497,6 +5238,11 @@
       </c>
       <c r="C256" s="2" t="inlineStr"/>
       <c r="D256" s="2" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>La comida principal del día en España es al mediodía.</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -4525,6 +5271,11 @@
       </c>
       <c r="C258" s="2" t="inlineStr"/>
       <c r="D258" s="2" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Mi compañero de trabajo me ayuda con las tareas difíciles.</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -4539,6 +5290,11 @@
       </c>
       <c r="C259" s="2" t="inlineStr"/>
       <c r="D259" s="2" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Trabajo para una compañía de seguros.</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -4685,6 +5441,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>El conductor del autobús para en cada parada.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -4703,6 +5464,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>El conejo tiene orejas largas y salta muy rápido.</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -4717,6 +5483,11 @@
       </c>
       <c r="C270" s="2" t="inlineStr"/>
       <c r="D270" s="2" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Tengo mucha confianza en mis propias habilidades.</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -4731,6 +5502,11 @@
       </c>
       <c r="C271" s="2" t="inlineStr"/>
       <c r="D271" s="2" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Puedo confiar en mis amigos cuando tengo problemas.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -4799,6 +5575,11 @@
       </c>
       <c r="C275" s="2" t="inlineStr"/>
       <c r="D275" s="2" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Es un actor muy conocido en todo el mundo.</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -4813,6 +5594,11 @@
       </c>
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Trabajé duro para conseguir este trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -4827,6 +5613,11 @@
       </c>
       <c r="C277" s="2" t="inlineStr"/>
       <c r="D277" s="2" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Le pido consejo a mi padre antes de tomar decisiones importantes.</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -4859,6 +5650,11 @@
       </c>
       <c r="C279" s="2" t="inlineStr"/>
       <c r="D279" s="2" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Perdí el contacto con mi amigo de la infancia.</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -4873,6 +5669,11 @@
       </c>
       <c r="C280" s="2" t="inlineStr"/>
       <c r="D280" s="2" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Me gusta contar historias a mis hijos antes de dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -4951,6 +5752,11 @@
       </c>
       <c r="C285" s="2" t="inlineStr"/>
       <c r="D285" s="2" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>No estoy enojado, al contrario, estoy muy feliz.</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -4965,6 +5771,11 @@
       </c>
       <c r="C286" s="2" t="inlineStr"/>
       <c r="D286" s="2" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Firmo el contrato antes de empezar el nuevo trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -4993,6 +5804,11 @@
       </c>
       <c r="C288" s="2" t="inlineStr"/>
       <c r="D288" s="2" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Tuvimos una conversación muy interesante sobre política.</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -5007,6 +5823,11 @@
       </c>
       <c r="C289" s="2" t="inlineStr"/>
       <c r="D289" s="2" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Brindamos con una copa de champán en la boda.</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -5025,6 +5846,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>El corazón bombea sangre por todo el cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -5043,6 +5869,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Me pongo una corbata para ir a una boda.</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -5057,6 +5888,11 @@
       </c>
       <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>El coronel es un rango militar superior al capitán.</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -5139,6 +5975,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Cierro la cortina para que no entre la luz del sol.</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -5221,6 +6062,11 @@
       </c>
       <c r="C302" s="2" t="inlineStr"/>
       <c r="D302" s="2" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>La policía investiga el crimen que ocurrió anoche.</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -5485,6 +6331,11 @@
       </c>
       <c r="C318" s="2" t="inlineStr"/>
       <c r="D318" s="2" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Mi cuarto tiene una cama y un escritorio.</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -5517,6 +6368,11 @@
       </c>
       <c r="C320" s="2" t="inlineStr"/>
       <c r="D320" s="2" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Corto el pan con un cuchillo afilado.</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -5535,6 +6391,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>La bufanda cubre el cuello.</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -5549,6 +6410,11 @@
       </c>
       <c r="C322" s="2" t="inlineStr"/>
       <c r="D322" s="2" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Pido la cuenta después de cenar en el restaurante.</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -5563,6 +6429,11 @@
       </c>
       <c r="C323" s="2" t="inlineStr"/>
       <c r="D323" s="2" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Hago ejercicio para mantener mi cuerpo sano.</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -5591,6 +6462,11 @@
       </c>
       <c r="C325" s="2" t="inlineStr"/>
       <c r="D325" s="2" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Ten cuidado al cruzar la calle.</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -5605,6 +6481,11 @@
       </c>
       <c r="C326" s="2" t="inlineStr"/>
       <c r="D326" s="2" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Tengo que cuidar a mi hermano pequeño esta tarde.</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -5619,6 +6500,11 @@
       </c>
       <c r="C327" s="2" t="inlineStr"/>
       <c r="D327" s="2" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Fue mi culpa que llegáramos tarde.</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -5633,6 +6519,11 @@
       </c>
       <c r="C328" s="2" t="inlineStr"/>
       <c r="D328" s="2" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>El jurado declaró culpable al acusado.</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -5647,6 +6538,11 @@
       </c>
       <c r="C329" s="2" t="inlineStr"/>
       <c r="D329" s="2" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Celebro mi cumpleaños con una fiesta cada año.</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -5665,6 +6561,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>¿Cuál de estos dos vestidos prefieres?</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -5683,6 +6584,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>¿Cuándo es tu cumpleaños?</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -5701,6 +6607,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>¿Cuánto cuesta este billete de tren?</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -5719,6 +6630,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>¿Cuántos hermanos tienes?</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -5755,6 +6671,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>La hermana de mi esposo es mi cuñada.</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -5773,6 +6694,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>El hermano de mi esposa es mi cuñado.</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -5787,6 +6713,11 @@
       </c>
       <c r="C337" s="2" t="inlineStr"/>
       <c r="D337" s="2" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Tomo fotos con mi cámara nueva.</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -5801,6 +6732,11 @@
       </c>
       <c r="C338" s="2" t="inlineStr"/>
       <c r="D338" s="2" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>El criminal fue condenado a diez años de cárcel.</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -5815,6 +6751,11 @@
       </c>
       <c r="C339" s="2" t="inlineStr"/>
       <c r="D339" s="2" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Escribo código para crear aplicaciones informáticas.</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -5833,6 +6774,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>¿Cómo te llamas?</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -5887,6 +6833,11 @@
       </c>
       <c r="C343" s="2" t="inlineStr"/>
       <c r="D343" s="2" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>La dama llevaba un vestido elegante en la fiesta real.</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -5933,6 +6884,11 @@
       </c>
       <c r="C346" s="2" t="inlineStr"/>
       <c r="D346" s="2" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>El terremoto causó mucho daño en la ciudad.</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -5993,6 +6949,11 @@
       </c>
       <c r="C350" s="2" t="inlineStr"/>
       <c r="D350" s="2" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>El vuelo se canceló debido a la tormenta.</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -6043,6 +7004,11 @@
       </c>
       <c r="C353" s="2" t="inlineStr"/>
       <c r="D353" s="2" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Tomo la decisión de estudiar medicina.</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -6061,6 +7027,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Llevo el anillo en el dedo.</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -6075,6 +7046,11 @@
       </c>
       <c r="C355" s="2" t="inlineStr"/>
       <c r="D355" s="2" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>El abogado presenta la defensa de su cliente en el juicio.</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -6139,6 +7115,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>El delfín salta y nada muy rápido en el mar.</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -6167,6 +7148,11 @@
       </c>
       <c r="C361" s="2" t="inlineStr"/>
       <c r="D361" s="2" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Dicen que el demonio vive en el infierno.</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -6223,6 +7209,11 @@
       </c>
       <c r="C365" s="2" t="inlineStr"/>
       <c r="D365" s="2" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>No quiero depender de nadie para ser feliz.</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -6237,6 +7228,11 @@
       </c>
       <c r="C366" s="2" t="inlineStr"/>
       <c r="D366" s="2" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Giro a la derecha en el próximo semáforo.</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -6265,6 +7261,11 @@
       </c>
       <c r="C368" s="2" t="inlineStr"/>
       <c r="D368" s="2" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>El niño desaparecido fue encontrado sano y salvo.</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -6279,6 +7280,11 @@
       </c>
       <c r="C369" s="2" t="inlineStr"/>
       <c r="D369" s="2" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>El huracán fue un desastre natural terrible.</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -6297,6 +7303,11 @@
           <t>dailyverbs</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Me gusta desayunar café con tostadas por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -6315,6 +7326,11 @@
           <t>dailyverbs</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Necesito descansar después de un día largo de trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -6329,6 +7345,11 @@
       </c>
       <c r="C372" s="2" t="inlineStr"/>
       <c r="D372" s="2" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Tomo un descanso de diez minutos durante el trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -6357,6 +7378,11 @@
       </c>
       <c r="C374" s="2" t="inlineStr"/>
       <c r="D374" s="2" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Quiero desear feliz cumpleaños a mi hermana.</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -6371,6 +7397,11 @@
       </c>
       <c r="C375" s="2" t="inlineStr"/>
       <c r="D375" s="2" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Mi deseo es viajar por todo el mundo algún día.</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -6385,6 +7416,11 @@
       </c>
       <c r="C376" s="2" t="inlineStr"/>
       <c r="D376" s="2" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Conduzco despacio porque está lloviendo.</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -6435,6 +7471,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Es difícil despertarse temprano los lunes.</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -6463,6 +7504,11 @@
       </c>
       <c r="C381" s="2" t="inlineStr"/>
       <c r="D381" s="2" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Nuestro destino final es la playa.</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -6477,6 +7523,11 @@
       </c>
       <c r="C382" s="2" t="inlineStr"/>
       <c r="D382" s="2" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Me fijo en cada detalle de la pintura.</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -6491,6 +7542,11 @@
       </c>
       <c r="C383" s="2" t="inlineStr"/>
       <c r="D383" s="2" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>El detective investiga el crimen para encontrar al culpable.</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -6505,6 +7561,11 @@
       </c>
       <c r="C384" s="2" t="inlineStr"/>
       <c r="D384" s="2" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>La policía va a detener al sospechoso.</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -6569,6 +7630,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Celebramos la Navidad en diciembre.</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -6659,6 +7725,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>El dentista cuida mis dientes.</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -6691,6 +7762,11 @@
       </c>
       <c r="C395" s="2" t="inlineStr"/>
       <c r="D395" s="2" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>No hay mucha diferencia entre estos dos productos.</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -6733,6 +7809,11 @@
       </c>
       <c r="C398" s="2" t="inlineStr"/>
       <c r="D398" s="2" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Necesito ganar más dinero para pagar el alquiler.</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -6747,6 +7828,11 @@
       </c>
       <c r="C399" s="2" t="inlineStr"/>
       <c r="D399" s="2" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Muchas personas rezan a Dios todos los días.</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -6761,6 +7847,11 @@
       </c>
       <c r="C400" s="2" t="inlineStr"/>
       <c r="D400" s="2" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Escribo mi dirección en el sobre antes de enviar la carta.</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -6789,6 +7880,11 @@
       </c>
       <c r="C402" s="2" t="inlineStr"/>
       <c r="D402" s="2" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>El director de la escuela habla con los padres.</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -6803,6 +7899,11 @@
       </c>
       <c r="C403" s="2" t="inlineStr"/>
       <c r="D403" s="2" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Le pido disculpas por llegar tarde.</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -6849,6 +7950,11 @@
       </c>
       <c r="C406" s="2" t="inlineStr"/>
       <c r="D406" s="2" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Vivo a poca distancia de mi trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -6863,6 +7969,11 @@
       </c>
       <c r="C407" s="2" t="inlineStr"/>
       <c r="D407" s="2" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>El partido de fútbol fue muy divertido.</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -6909,6 +8020,11 @@
       </c>
       <c r="C410" s="2" t="inlineStr"/>
       <c r="D410" s="2" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>El doctor me receta medicinas para la gripe.</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -6923,6 +8039,11 @@
       </c>
       <c r="C411" s="2" t="inlineStr"/>
       <c r="D411" s="2" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Empezó a doler la muela por la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -6937,6 +8058,11 @@
       </c>
       <c r="C412" s="2" t="inlineStr"/>
       <c r="D412" s="2" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Tomo una aspirina para el dolor de cabeza.</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -6955,6 +8081,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>El domingo es el último día de la semana.</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -7001,6 +8132,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>El anillo es de oro, de color dorado.</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -7019,6 +8155,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Necesito dormir ocho horas cada noche.</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -7055,6 +8196,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Mi dormitorio tiene una cama, un armario y una ventana.</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -7087,6 +8233,11 @@
       </c>
       <c r="C421" s="2" t="inlineStr"/>
       <c r="D421" s="2" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>La policía confiscó droga ilegal durante la redada.</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -7105,6 +8256,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Es agradable ducharse con agua caliente por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -7119,6 +8275,11 @@
       </c>
       <c r="C423" s="2" t="inlineStr"/>
       <c r="D423" s="2" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Tengo una duda sobre la tarea de matemáticas.</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -7133,6 +8294,11 @@
       </c>
       <c r="C424" s="2" t="inlineStr"/>
       <c r="D424" s="2" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Como un postre dulce después de la cena.</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -7175,6 +8341,11 @@
       </c>
       <c r="C427" s="2" t="inlineStr"/>
       <c r="D427" s="2" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Trabajo ocho horas al día de lunes a viernes.</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -7189,6 +8360,11 @@
       </c>
       <c r="C428" s="2" t="inlineStr"/>
       <c r="D428" s="2" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Cambio euros por dólares en el banco.</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -7207,6 +8383,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>¿Dónde está el baño?</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -7235,6 +8416,11 @@
       </c>
       <c r="C431" s="2" t="inlineStr"/>
       <c r="D431" s="2" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Mi abuela tiene ochenta años de edad.</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -7249,6 +8435,11 @@
       </c>
       <c r="C432" s="2" t="inlineStr"/>
       <c r="D432" s="2" t="inlineStr"/>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Trabajo en un edificio de oficinas en el centro.</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -7263,6 +8454,11 @@
       </c>
       <c r="C433" s="2" t="inlineStr"/>
       <c r="D433" s="2" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>El profesor da un ejemplo para explicar la lección.</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -7277,6 +8473,11 @@
       </c>
       <c r="C434" s="2" t="inlineStr"/>
       <c r="D434" s="2" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>El ejército protege las fronteras del país.</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -7291,6 +8492,11 @@
       </c>
       <c r="C435" s="2" t="inlineStr"/>
       <c r="D435" s="2" t="inlineStr"/>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>El resultado de la elección sorprendió a todos.</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -7309,6 +8515,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>El elefante es el animal terrestre más grande.</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -7365,6 +8576,11 @@
       </c>
       <c r="C440" s="2" t="inlineStr"/>
       <c r="D440" s="2" t="inlineStr"/>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Mi hermana está embarazada de su primer hijo.</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -7379,6 +8595,11 @@
       </c>
       <c r="C441" s="2" t="inlineStr"/>
       <c r="D441" s="2" t="inlineStr"/>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>No tengo hambre; sin embargo, voy a comer algo.</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -7393,6 +8614,11 @@
       </c>
       <c r="C442" s="2" t="inlineStr"/>
       <c r="D442" s="2" t="inlineStr"/>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Llamo al número de emergencia si hay un incendio.</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -7443,6 +8669,11 @@
       </c>
       <c r="C445" s="2" t="inlineStr"/>
       <c r="D445" s="2" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Trabajo para una empresa de tecnología.</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -7603,6 +8834,11 @@
       </c>
       <c r="C455" s="2" t="inlineStr"/>
       <c r="D455" s="2" t="inlineStr"/>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>El ejército lucha contra el enemigo en la guerra.</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -7617,6 +8853,11 @@
       </c>
       <c r="C456" s="2" t="inlineStr"/>
       <c r="D456" s="2" t="inlineStr"/>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Como bien para tener energía durante el día.</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -7635,6 +8876,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>El primer mes del año es enero.</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -7649,6 +8895,11 @@
       </c>
       <c r="C458" s="2" t="inlineStr"/>
       <c r="D458" s="2" t="inlineStr"/>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>El médico trata la enfermedad con medicinas.</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -7663,6 +8914,11 @@
       </c>
       <c r="C459" s="2" t="inlineStr"/>
       <c r="D459" s="2" t="inlineStr"/>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Me quedo en casa porque estoy enfermo.</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -7713,6 +8969,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Corto lechuga y tomate para hacer una ensalada.</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -7791,6 +9052,11 @@
       </c>
       <c r="C467" s="2" t="inlineStr"/>
       <c r="D467" s="2" t="inlineStr"/>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Compro una entrada para el concierto de mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -7855,6 +9121,11 @@
       </c>
       <c r="C471" s="2" t="inlineStr"/>
       <c r="D471" s="2" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Mi equipo de fútbol ganó el partido ayer.</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -7869,6 +9140,11 @@
       </c>
       <c r="C472" s="2" t="inlineStr"/>
       <c r="D472" s="2" t="inlineStr"/>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Creo que estás equivocado sobre este tema.</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -7883,6 +9159,11 @@
       </c>
       <c r="C473" s="2" t="inlineStr"/>
       <c r="D473" s="2" t="inlineStr"/>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Cometí un error en el examen de matemáticas.</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -7897,6 +9178,11 @@
       </c>
       <c r="C474" s="2" t="inlineStr"/>
       <c r="D474" s="2" t="inlineStr"/>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>El prisionero intentó escapar de la cárcel.</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -7911,6 +9197,11 @@
       </c>
       <c r="C475" s="2" t="inlineStr"/>
       <c r="D475" s="2" t="inlineStr"/>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>El actor filma una escena de la película.</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -7929,6 +9220,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Me gusta escribir cartas a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -7947,6 +9243,11 @@
           <t>dailyverbs</t>
         </is>
       </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Me gusta escuchar música mientras cocino.</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -7961,6 +9262,11 @@
       </c>
       <c r="C478" s="2" t="inlineStr"/>
       <c r="D478" s="2" t="inlineStr"/>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Los niños aprenden a leer y escribir en la escuela.</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -7989,6 +9295,11 @@
       </c>
       <c r="C480" s="2" t="inlineStr"/>
       <c r="D480" s="2" t="inlineStr"/>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Los astronautas viajan al espacio en un cohete.</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -8007,6 +9318,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Llevo la mochila en la espalda.</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -8049,6 +9365,11 @@
       </c>
       <c r="C484" s="2" t="inlineStr"/>
       <c r="D484" s="2" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>El panda es una especie en peligro de extinción.</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -8063,6 +9384,11 @@
       </c>
       <c r="C485" s="2" t="inlineStr"/>
       <c r="D485" s="2" t="inlineStr"/>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Vamos a ver un espectáculo de magia esta noche.</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -8081,6 +9407,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Me miro en el espejo para peinarme.</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -8095,6 +9426,11 @@
       </c>
       <c r="C487" s="2" t="inlineStr"/>
       <c r="D487" s="2" t="inlineStr"/>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Nunca pierdo la esperanza de un futuro mejor.</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -8131,6 +9467,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>La mujer con la que me casé es mi esposa.</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -8149,6 +9490,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>El hombre con el que me casé es mi esposo.</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -8181,6 +9527,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Espero el tren en el andén de la estación.</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -8213,6 +9564,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Coloco mis libros en la estantería.</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -8263,6 +9619,11 @@
       </c>
       <c r="C497" s="2" t="inlineStr"/>
       <c r="D497" s="2" t="inlineStr"/>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Ella tiene un estilo de ropa muy elegante.</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -8277,6 +9638,11 @@
       </c>
       <c r="C498" s="2" t="inlineStr"/>
       <c r="D498" s="2" t="inlineStr"/>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Las estrellas brillan en el cielo por la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -8313,6 +9679,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Necesito estudiar mucho para aprobar el examen.</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -8359,6 +9730,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Llevo el paraguas porque está lloviendo.</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -8377,6 +9753,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Los niños hacen un muñeco porque está nevando.</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -8395,6 +9776,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>No veo el sol porque está nublado.</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -8413,6 +9799,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>La comida baja al estómago.</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -8441,6 +9832,11 @@
       </c>
       <c r="C508" s="2" t="inlineStr"/>
       <c r="D508" s="2" t="inlineStr"/>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>La policía encontró evidencia del crimen.</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -8455,6 +9851,11 @@
       </c>
       <c r="C509" s="2" t="inlineStr"/>
       <c r="D509" s="2" t="inlineStr"/>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Intento evitar el tráfico saliendo temprano.</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -8539,6 +9940,11 @@
       </c>
       <c r="C515" s="2" t="inlineStr"/>
       <c r="D515" s="2" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Tengo diez años de experiencia en este trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -8571,6 +9977,11 @@
       </c>
       <c r="C517" s="2" t="inlineStr"/>
       <c r="D517" s="2" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Escuché un ruido extraño en la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -8589,6 +10000,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>La falda le llega hasta la rodilla.</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -8621,6 +10037,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Toda mi familia se reúne en Navidad.</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -8635,6 +10056,11 @@
       </c>
       <c r="C521" s="2" t="inlineStr"/>
       <c r="D521" s="2" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Voy a visitar a un familiar que vive lejos.</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -8663,6 +10089,11 @@
       </c>
       <c r="C523" s="2" t="inlineStr"/>
       <c r="D523" s="2" t="inlineStr"/>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Te pido un favor, ¿puedes ayudarme con esto?</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -8677,6 +10108,11 @@
       </c>
       <c r="C524" s="2" t="inlineStr"/>
       <c r="D524" s="2" t="inlineStr"/>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Tiene mucha fe en que todo saldrá bien.</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -8695,6 +10131,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Febrero es el mes más corto del año.</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -8727,6 +10168,11 @@
       </c>
       <c r="C527" s="2" t="inlineStr"/>
       <c r="D527" s="2" t="inlineStr"/>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Vamos a una fiesta de cumpleaños esta noche.</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -8741,6 +10187,11 @@
       </c>
       <c r="C528" s="2" t="inlineStr"/>
       <c r="D528" s="2" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Descanso mucho durante el fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -8783,6 +10234,11 @@
       </c>
       <c r="C531" s="2" t="inlineStr"/>
       <c r="D531" s="2" t="inlineStr"/>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Le regalo una flor roja a mi novia.</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -8825,6 +10281,11 @@
       </c>
       <c r="C534" s="2" t="inlineStr"/>
       <c r="D534" s="2" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Tomo una foto del paisaje con mi cámara.</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -8857,6 +10318,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>La fresa es una fruta roja con semillas por fuera.</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -8875,6 +10341,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>La manzana y el plátano son mi fruta favorita.</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -8889,6 +10360,11 @@
       </c>
       <c r="C538" s="2" t="inlineStr"/>
       <c r="D538" s="2" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Tiemblo de frío porque no llevo abrigo.</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -8903,6 +10379,11 @@
       </c>
       <c r="C539" s="2" t="inlineStr"/>
       <c r="D539" s="2" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Los bomberos apagan el fuego del incendio.</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -8931,6 +10412,11 @@
       </c>
       <c r="C541" s="2" t="inlineStr"/>
       <c r="D541" s="2" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Necesito mucha fuerza para levantar esta caja pesada.</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -8945,6 +10431,11 @@
       </c>
       <c r="C542" s="2" t="inlineStr"/>
       <c r="D542" s="2" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Mi teléfono no quiere funcionar después de la actualización.</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -8963,6 +10454,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>El repartidor entrega los paquetes en su furgoneta.</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -8977,6 +10473,11 @@
       </c>
       <c r="C544" s="2" t="inlineStr"/>
       <c r="D544" s="2" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Pienso mucho en mi futuro y mi carrera.</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -9009,6 +10510,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>La gallina pone un huevo cada día.</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -9023,6 +10529,11 @@
       </c>
       <c r="C547" s="2" t="inlineStr"/>
       <c r="D547" s="2" t="inlineStr"/>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>No tengo ganas de salir hoy.</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -9037,6 +10548,11 @@
       </c>
       <c r="C548" s="2" t="inlineStr"/>
       <c r="D548" s="2" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Quiero ganar el partido de tenis mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -9055,6 +10571,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Aparco el coche en el garaje.</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -9073,6 +10594,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Me duele la garganta cuando tengo un resfriado.</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -9109,6 +10635,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>El gato caza ratones por la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -9137,6 +10668,11 @@
       </c>
       <c r="C554" s="2" t="inlineStr"/>
       <c r="D554" s="2" t="inlineStr"/>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>El general dirige todo el ejército del país.</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -9165,6 +10701,11 @@
       </c>
       <c r="C556" s="2" t="inlineStr"/>
       <c r="D556" s="2" t="inlineStr"/>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Hay mucha gente en la calle hoy.</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -9179,6 +10720,11 @@
       </c>
       <c r="C557" s="2" t="inlineStr"/>
       <c r="D557" s="2" t="inlineStr"/>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>El gobierno anuncia nuevas leyes este año.</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -9193,6 +10739,11 @@
       </c>
       <c r="C558" s="2" t="inlineStr"/>
       <c r="D558" s="2" t="inlineStr"/>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Recibí un golpe en la cabeza jugando fútbol.</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -9249,6 +10800,11 @@
       </c>
       <c r="C562" s="2" t="inlineStr"/>
       <c r="D562" s="2" t="inlineStr"/>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Vivo en una casa grande con jardín.</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -9267,6 +10823,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>El cielo está gris antes de la tormenta.</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -9299,6 +10860,11 @@
       </c>
       <c r="C565" s="2" t="inlineStr"/>
       <c r="D565" s="2" t="inlineStr"/>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Trabajamos en grupo para terminar el proyecto.</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -9317,6 +10883,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Me pongo los guantes para no tener frío en las manos.</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -9331,6 +10902,11 @@
       </c>
       <c r="C567" s="2" t="inlineStr"/>
       <c r="D567" s="2" t="inlineStr"/>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>El guardia de seguridad vigila la entrada del edificio.</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -9345,6 +10921,11 @@
       </c>
       <c r="C568" s="2" t="inlineStr"/>
       <c r="D568" s="2" t="inlineStr"/>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Muchos soldados murieron en la guerra.</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -9431,6 +11012,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Me gusta hablar varios idiomas.</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -9449,6 +11035,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Voy a la piscina porque hace calor.</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -9467,6 +11058,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Enciendo la chimenea porque hace frío.</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -9485,6 +11081,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Me pongo gafas de sol porque hace sol.</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -9503,6 +11104,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Las hojas de los árboles se mueven porque hace viento.</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -9521,6 +11127,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Tengo mucho que hacer hoy.</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -9549,6 +11160,11 @@
       </c>
       <c r="C580" s="2" t="inlineStr"/>
       <c r="D580" s="2" t="inlineStr"/>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Como algo porque tengo mucha hambre.</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -9653,6 +11269,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>No puedo ver bien la carretera porque hay niebla.</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -9685,6 +11306,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>El helicóptero despega verticalmente sin necesitar pista.</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -9699,6 +11325,11 @@
       </c>
       <c r="C589" s="2" t="inlineStr"/>
       <c r="D589" s="2" t="inlineStr"/>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>El médico cura la herida del paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
@@ -9731,6 +11362,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>La hija de mis padres es mi hermana.</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -9749,6 +11385,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>El hijo de mis padres es mi hermano.</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
@@ -9781,6 +11422,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>El agua se convierte en hielo cuando hace mucho frío.</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -9799,6 +11445,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Soy el padre de mi hija, una niña de ocho años.</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -9817,6 +11468,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Soy el padre de mi hijo, un niño de ocho años.</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -9831,6 +11487,11 @@
       </c>
       <c r="C597" s="2" t="inlineStr"/>
       <c r="D597" s="2" t="inlineStr"/>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Estudio la historia de mi país en la universidad.</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -9845,6 +11506,11 @@
       </c>
       <c r="C598" s="2" t="inlineStr"/>
       <c r="D598" s="2" t="inlineStr"/>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Después de viajar, siempre es bueno volver al hogar.</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -9877,6 +11543,11 @@
       </c>
       <c r="C600" s="2" t="inlineStr"/>
       <c r="D600" s="2" t="inlineStr"/>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>El hombre lleva un traje negro a la boda.</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
@@ -9895,6 +11566,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Llevo el bolso en el hombro.</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -9923,6 +11599,11 @@
       </c>
       <c r="C603" s="2" t="inlineStr"/>
       <c r="D603" s="2" t="inlineStr"/>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Llego a mi cita a la hora exacta.</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -9941,6 +11622,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>La hormiga es muy pequeña pero muy fuerte para su tamaño.</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -9969,6 +11655,11 @@
       </c>
       <c r="C606" s="2" t="inlineStr"/>
       <c r="D606" s="2" t="inlineStr"/>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Llevan al herido al hospital en ambulancia.</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -9983,6 +11674,11 @@
       </c>
       <c r="C607" s="2" t="inlineStr"/>
       <c r="D607" s="2" t="inlineStr"/>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Reservamos una habitación en el hotel para las vacaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
@@ -9997,6 +11693,11 @@
       </c>
       <c r="C608" s="2" t="inlineStr"/>
       <c r="D608" s="2" t="inlineStr"/>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Hoy hace mucho sol y calor.</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
@@ -10011,6 +11712,11 @@
       </c>
       <c r="C609" s="2" t="inlineStr"/>
       <c r="D609" s="2" t="inlineStr"/>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>El detective encuentra una huella dactilar en la escena del crimen.</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -10029,6 +11735,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>El perro juega con un hueso.</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
@@ -10047,6 +11758,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Rompo un huevo para hacer una tortilla.</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -10061,6 +11777,11 @@
       </c>
       <c r="C612" s="2" t="inlineStr"/>
       <c r="D612" s="2" t="inlineStr"/>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>El cuerpo humano tiene muchos huesos.</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -10089,6 +11810,11 @@
       </c>
       <c r="C614" s="2" t="inlineStr"/>
       <c r="D614" s="2" t="inlineStr"/>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>El héroe salva a la ciudad del peligro.</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -10103,6 +11829,11 @@
       </c>
       <c r="C615" s="2" t="inlineStr"/>
       <c r="D615" s="2" t="inlineStr"/>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Tengo una idea genial para el proyecto.</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
@@ -10131,6 +11862,11 @@
       </c>
       <c r="C617" s="2" t="inlineStr"/>
       <c r="D617" s="2" t="inlineStr"/>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Vamos a la iglesia todos los domingos.</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -10159,6 +11895,11 @@
       </c>
       <c r="C619" s="2" t="inlineStr"/>
       <c r="D619" s="2" t="inlineStr"/>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Busco una imagen para poner en la presentación.</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -10243,6 +11984,11 @@
       </c>
       <c r="C625" s="2" t="inlineStr"/>
       <c r="D625" s="2" t="inlineStr"/>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Hace tanto calor aquí que parece el infierno.</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -10257,6 +12003,11 @@
       </c>
       <c r="C626" s="2" t="inlineStr"/>
       <c r="D626" s="2" t="inlineStr"/>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Busco información sobre el nuevo trabajo en internet.</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -10271,6 +12022,11 @@
       </c>
       <c r="C627" s="2" t="inlineStr"/>
       <c r="D627" s="2" t="inlineStr"/>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Escribo un informe sobre las ventas del mes.</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -10285,6 +12041,11 @@
       </c>
       <c r="C628" s="2" t="inlineStr"/>
       <c r="D628" s="2" t="inlineStr"/>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Estudio inglés porque quiero trabajar en Londres.</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -10327,6 +12088,11 @@
       </c>
       <c r="C631" s="2" t="inlineStr"/>
       <c r="D631" s="2" t="inlineStr"/>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>El jurado declaró inocente al acusado.</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -10341,6 +12107,11 @@
       </c>
       <c r="C632" s="2" t="inlineStr"/>
       <c r="D632" s="2" t="inlineStr"/>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>El inspector de policía interroga al sospechoso.</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
@@ -10369,6 +12140,11 @@
       </c>
       <c r="C634" s="2" t="inlineStr"/>
       <c r="D634" s="2" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>No tengo intención de mentirte.</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -10457,6 +12233,11 @@
       </c>
       <c r="C640" s="2" t="inlineStr"/>
       <c r="D640" s="2" t="inlineStr"/>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>La policía abre una investigación sobre el robo.</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -10493,6 +12274,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Quiero ir al cine este fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -10507,6 +12293,11 @@
       </c>
       <c r="C643" s="2" t="inlineStr"/>
       <c r="D643" s="2" t="inlineStr"/>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Pasamos las vacaciones en una isla tropical.</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -10521,6 +12312,11 @@
       </c>
       <c r="C644" s="2" t="inlineStr"/>
       <c r="D644" s="2" t="inlineStr"/>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Giro a la izquierda en la próxima calle.</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -10553,6 +12349,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Riego las plantas del jardín cada mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -10567,6 +12368,11 @@
       </c>
       <c r="C647" s="2" t="inlineStr"/>
       <c r="D647" s="2" t="inlineStr"/>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Mi jefe me da más trabajo cada semana.</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -10585,6 +12391,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>La jirafa tiene el cuello más largo de todos los animales.</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -10599,6 +12410,11 @@
       </c>
       <c r="C649" s="2" t="inlineStr"/>
       <c r="D649" s="2" t="inlineStr"/>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Mi abuelo todavía se siente joven a pesar de su edad.</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
@@ -10613,6 +12429,11 @@
       </c>
       <c r="C650" s="2" t="inlineStr"/>
       <c r="D650" s="2" t="inlineStr"/>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>A los niños les gusta este juego de mesa.</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
@@ -10631,6 +12452,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>El jueves está entre el miércoles y el viernes.</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="inlineStr">
@@ -10645,6 +12471,11 @@
       </c>
       <c r="C652" s="2" t="inlineStr"/>
       <c r="D652" s="2" t="inlineStr"/>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>El juez decide la sentencia en el juicio.</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
@@ -10663,6 +12494,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>A los niños les encanta jugar en el parque.</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -10681,6 +12517,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Exprimo naranjas para hacer jugo.</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
@@ -10695,6 +12536,11 @@
       </c>
       <c r="C655" s="2" t="inlineStr"/>
       <c r="D655" s="2" t="inlineStr"/>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>El acusado espera el resultado del juicio.</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -10713,6 +12559,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Julio es uno de los meses más calurosos del verano.</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -10731,6 +12582,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>El verano empieza en junio.</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -10759,6 +12615,11 @@
       </c>
       <c r="C659" s="2" t="inlineStr"/>
       <c r="D659" s="2" t="inlineStr"/>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Doce personas forman el jurado en este juicio.</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -10773,6 +12634,11 @@
       </c>
       <c r="C660" s="2" t="inlineStr"/>
       <c r="D660" s="2" t="inlineStr"/>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Tengo que jurar decir la verdad ante el juez.</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -10787,6 +12653,11 @@
       </c>
       <c r="C661" s="2" t="inlineStr"/>
       <c r="D661" s="2" t="inlineStr"/>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>El juez busca hacer justicia en este caso.</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -10819,6 +12690,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Se pinta los labios de color rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -10833,6 +12709,11 @@
       </c>
       <c r="C664" s="2" t="inlineStr"/>
       <c r="D664" s="2" t="inlineStr"/>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>El científico hace experimentos en el laboratorio.</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -10875,6 +12756,11 @@
       </c>
       <c r="C667" s="2" t="inlineStr"/>
       <c r="D667" s="2" t="inlineStr"/>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>El río más largo del mundo está en Sudamérica.</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="inlineStr">
@@ -10911,6 +12797,11 @@
           <t>dailyverbs</t>
         </is>
       </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Es importante lavarse las manos antes de comer.</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
@@ -10929,6 +12820,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Pongo leche en el café por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -10947,6 +12843,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Necesito gafas para leer el periódico.</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -10979,6 +12880,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Pruebo la comida con la lengua.</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="2" t="inlineStr">
@@ -10997,6 +12903,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Cuesta mucho levantarse de la cama los lunes por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="inlineStr">
@@ -11011,6 +12922,11 @@
       </c>
       <c r="C675" s="2" t="inlineStr"/>
       <c r="D675" s="2" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>El congreso aprueba una nueva ley este año.</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="2" t="inlineStr">
@@ -11029,6 +12945,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>El león es el rey de la selva.</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -11043,6 +12964,11 @@
       </c>
       <c r="C677" s="2" t="inlineStr"/>
       <c r="D677" s="2" t="inlineStr"/>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Los presos sueñan con la libertad.</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
@@ -11071,6 +12997,11 @@
       </c>
       <c r="C679" s="2" t="inlineStr"/>
       <c r="D679" s="2" t="inlineStr"/>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Leo un libro nuevo cada mes.</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
@@ -11089,6 +13020,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>La flor llamada lila le da su nombre a este color.</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
@@ -11107,6 +13043,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Necesito limpiar la casa antes de que lleguen los invitados.</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -11135,6 +13076,11 @@
       </c>
       <c r="C683" s="2" t="inlineStr"/>
       <c r="D683" s="2" t="inlineStr"/>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Hago una lista de la compra antes de ir al supermercado.</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -11163,6 +13109,11 @@
       </c>
       <c r="C685" s="2" t="inlineStr"/>
       <c r="D685" s="2" t="inlineStr"/>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Recibo una llamada importante de mi jefe.</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -11195,6 +13146,11 @@
       </c>
       <c r="C687" s="2" t="inlineStr"/>
       <c r="D687" s="2" t="inlineStr"/>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Abro la puerta con la llave de casa.</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
@@ -11227,6 +13183,11 @@
       </c>
       <c r="C689" s="2" t="inlineStr"/>
       <c r="D689" s="2" t="inlineStr"/>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>El autobús está lleno de gente por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -11299,6 +13260,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Llevo el paraguas para protegerme de la lluvia.</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -11317,6 +13283,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>El lobo aúlla a la luna por la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -11331,6 +13302,11 @@
       </c>
       <c r="C695" s="2" t="inlineStr"/>
       <c r="D695" s="2" t="inlineStr"/>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Está loco de alegría porque ganó la lotería.</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -11359,6 +13335,11 @@
       </c>
       <c r="C697" s="2" t="inlineStr"/>
       <c r="D697" s="2" t="inlineStr"/>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>La lucha por la libertad duró muchos años.</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
@@ -11373,6 +13354,11 @@
       </c>
       <c r="C698" s="2" t="inlineStr"/>
       <c r="D698" s="2" t="inlineStr"/>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Están dispuestos a luchar por defender su país.</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -11401,6 +13387,11 @@
       </c>
       <c r="C700" s="2" t="inlineStr"/>
       <c r="D700" s="2" t="inlineStr"/>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Este restaurante es mi lugar favorito para cenar.</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -11415,6 +13406,11 @@
       </c>
       <c r="C701" s="2" t="inlineStr"/>
       <c r="D701" s="2" t="inlineStr"/>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>La luna brilla en el cielo nocturno.</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
@@ -11433,6 +13429,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>El lunes es el primer día de la semana laboral.</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -11447,6 +13448,11 @@
       </c>
       <c r="C703" s="2" t="inlineStr"/>
       <c r="D703" s="2" t="inlineStr"/>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Enciendo la luz porque está muy oscuro.</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -11465,6 +13471,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Enciendo la lámpara para poder leer de noche.</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="inlineStr">
@@ -11479,6 +13490,11 @@
       </c>
       <c r="C705" s="2" t="inlineStr"/>
       <c r="D705" s="2" t="inlineStr"/>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>El líder del grupo toma las decisiones importantes.</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -11511,6 +13527,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>La mujer que me dio la vida es mi madre.</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -11525,6 +13546,11 @@
       </c>
       <c r="C708" s="2" t="inlineStr"/>
       <c r="D708" s="2" t="inlineStr"/>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>El maestro enseña matemáticas a los niños.</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -11539,6 +13565,11 @@
       </c>
       <c r="C709" s="2" t="inlineStr"/>
       <c r="D709" s="2" t="inlineStr"/>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>El mago hace un truco de magia en el escenario.</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -11581,6 +13612,11 @@
       </c>
       <c r="C712" s="2" t="inlineStr"/>
       <c r="D712" s="2" t="inlineStr"/>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>El brujo lanza una maldición sobre el pueblo.</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -11623,6 +13659,11 @@
       </c>
       <c r="C715" s="2" t="inlineStr"/>
       <c r="D715" s="2" t="inlineStr"/>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Mi mamá cocina la cena todas las noches.</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -11687,6 +13728,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Levanto la mano para preguntar.</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="2" t="inlineStr">
@@ -11701,6 +13747,11 @@
       </c>
       <c r="C720" s="2" t="inlineStr"/>
       <c r="D720" s="2" t="inlineStr"/>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Hago ejercicio para mantener mi salud.</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -11719,6 +13770,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Unto mantequilla en el pan tostado.</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
@@ -11737,6 +13793,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Como una manzana roja como postre.</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="inlineStr">
@@ -11751,6 +13812,11 @@
       </c>
       <c r="C723" s="2" t="inlineStr"/>
       <c r="D723" s="2" t="inlineStr"/>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Nadamos en el mar durante las vacaciones de verano.</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
@@ -11811,6 +13877,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>La oruga se convierte en mariposa.</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="inlineStr">
@@ -11829,6 +13900,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>El chocolate es de color marrón.</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="inlineStr">
@@ -11847,6 +13923,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>El martes está entre el lunes y el miércoles.</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="inlineStr">
@@ -11865,6 +13946,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>La primavera empieza en marzo.</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="inlineStr">
@@ -11879,6 +13965,11 @@
       </c>
       <c r="C731" s="2" t="inlineStr"/>
       <c r="D731" s="2" t="inlineStr"/>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>El soldado no quiere matar a nadie.</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="inlineStr">
@@ -11893,6 +13984,11 @@
       </c>
       <c r="C732" s="2" t="inlineStr"/>
       <c r="D732" s="2" t="inlineStr"/>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Después de diez años de matrimonio, siguen muy enamorados.</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -11911,6 +14007,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Mayo está entre abril y junio.</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="inlineStr">
@@ -11939,6 +14040,11 @@
       </c>
       <c r="C735" s="2" t="inlineStr"/>
       <c r="D735" s="2" t="inlineStr"/>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>La mayoría de los estudiantes aprobó el examen.</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="inlineStr">
@@ -11953,6 +14059,11 @@
       </c>
       <c r="C736" s="2" t="inlineStr"/>
       <c r="D736" s="2" t="inlineStr"/>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Mañana voy a visitar a mis abuelos.</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="2" t="inlineStr">
@@ -11985,6 +14096,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Le doy un beso en la mejilla.</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -12013,6 +14129,11 @@
       </c>
       <c r="C740" s="2" t="inlineStr"/>
       <c r="D740" s="2" t="inlineStr"/>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Tengo buena memoria para recordar nombres.</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="inlineStr">
@@ -12041,6 +14162,11 @@
       </c>
       <c r="C742" s="2" t="inlineStr"/>
       <c r="D742" s="2" t="inlineStr"/>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Te envío un mensaje por el teléfono.</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="inlineStr">
@@ -12055,6 +14181,11 @@
       </c>
       <c r="C743" s="2" t="inlineStr"/>
       <c r="D743" s="2" t="inlineStr"/>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Necesito relajar la mente después de un día difícil.</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -12069,6 +14200,11 @@
       </c>
       <c r="C744" s="2" t="inlineStr"/>
       <c r="D744" s="2" t="inlineStr"/>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Decir una mentira no está bien.</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -12083,6 +14219,11 @@
       </c>
       <c r="C745" s="2" t="inlineStr"/>
       <c r="D745" s="2" t="inlineStr"/>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Voy al gimnasio a menudo.</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
@@ -12097,6 +14238,11 @@
       </c>
       <c r="C746" s="2" t="inlineStr"/>
       <c r="D746" s="2" t="inlineStr"/>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Compro fruta fresca en el mercado los sábados.</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -12111,6 +14257,11 @@
       </c>
       <c r="C747" s="2" t="inlineStr"/>
       <c r="D747" s="2" t="inlineStr"/>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Recibo mi salario a final de mes.</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="inlineStr">
@@ -12129,6 +14280,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Ponemos los platos en la mesa antes de comer.</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="inlineStr">
@@ -12165,6 +14321,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Bajo las escaleras para coger el metro bajo la ciudad.</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="inlineStr">
@@ -12211,6 +14372,11 @@
       </c>
       <c r="C753" s="2" t="inlineStr"/>
       <c r="D753" s="2" t="inlineStr"/>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Tengo mucho miedo a las arañas.</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="inlineStr">
@@ -12253,6 +14419,11 @@
       </c>
       <c r="C756" s="2" t="inlineStr"/>
       <c r="D756" s="2" t="inlineStr"/>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Gana casi un millón de dólares al año.</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="inlineStr">
@@ -12267,6 +14438,11 @@
       </c>
       <c r="C757" s="2" t="inlineStr"/>
       <c r="D757" s="2" t="inlineStr"/>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>El ministro de educación anuncia cambios en las escuelas.</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="inlineStr">
@@ -12281,6 +14457,11 @@
       </c>
       <c r="C758" s="2" t="inlineStr"/>
       <c r="D758" s="2" t="inlineStr"/>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Espero solo un minuto y ya vuelvo.</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="inlineStr">
@@ -12313,6 +14494,11 @@
       </c>
       <c r="C760" s="2" t="inlineStr"/>
       <c r="D760" s="2" t="inlineStr"/>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>El astronauta cumple su misión en el espacio.</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -12341,6 +14527,11 @@
       </c>
       <c r="C762" s="2" t="inlineStr"/>
       <c r="D762" s="2" t="inlineStr"/>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Como solo la mitad del sándwich porque no tengo mucha hambre.</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="inlineStr">
@@ -12359,6 +14550,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>El miércoles es el día justo en medio de la semana.</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="inlineStr">
@@ -12387,6 +14583,11 @@
       </c>
       <c r="C765" s="2" t="inlineStr"/>
       <c r="D765" s="2" t="inlineStr"/>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>No quiero molestar a mis vecinos con el ruido.</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="inlineStr">
@@ -12419,6 +14620,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>El mono se columpia de árbol en árbol.</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="inlineStr">
@@ -12433,6 +14639,11 @@
       </c>
       <c r="C768" s="2" t="inlineStr"/>
       <c r="D768" s="2" t="inlineStr"/>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>El niño tiene miedo de que haya un monstruo debajo de la cama.</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="2" t="inlineStr">
@@ -12465,6 +14676,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>La berenjena es de color morado.</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="inlineStr">
@@ -12501,6 +14717,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Las moscas se sienten atraídas por la comida en mal estado.</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="inlineStr">
@@ -12551,6 +14772,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Se pone el casco antes de montar en la motocicleta.</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="inlineStr">
@@ -12665,6 +14891,11 @@
       </c>
       <c r="C782" s="2" t="inlineStr"/>
       <c r="D782" s="2" t="inlineStr"/>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>La muerte de su abuelo lo entristeció mucho.</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" s="2" t="inlineStr">
@@ -12693,6 +14924,11 @@
       </c>
       <c r="C784" s="2" t="inlineStr"/>
       <c r="D784" s="2" t="inlineStr"/>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>La mujer lleva un vestido elegante a la boda.</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="2" t="inlineStr">
@@ -12707,6 +14943,11 @@
       </c>
       <c r="C785" s="2" t="inlineStr"/>
       <c r="D785" s="2" t="inlineStr"/>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>China es el país con más habitantes del mundo.</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">
@@ -12739,6 +14980,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>El reloj se lleva en la muñeca.</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="2" t="inlineStr">
@@ -12753,6 +14999,11 @@
       </c>
       <c r="C788" s="2" t="inlineStr"/>
       <c r="D788" s="2" t="inlineStr"/>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>La máquina de lavar limpia la ropa automáticamente.</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="inlineStr">
@@ -12827,6 +15078,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Hago ejercicio para fortalecer los músculos.</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="2" t="inlineStr">
@@ -12841,6 +15097,11 @@
       </c>
       <c r="C794" s="2" t="inlineStr"/>
       <c r="D794" s="2" t="inlineStr"/>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>La música clásica me ayuda a relajarme.</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="inlineStr">
@@ -12919,6 +15180,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>La naranja es una fruta de color naranja.</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" s="2" t="inlineStr">
@@ -12937,6 +15203,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Huelo las flores con la nariz.</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="inlineStr">
@@ -12951,6 +15222,11 @@
       </c>
       <c r="C801" s="2" t="inlineStr"/>
       <c r="D801" s="2" t="inlineStr"/>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Me encanta pasear por la naturaleza los fines de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="inlineStr">
@@ -12965,6 +15241,11 @@
       </c>
       <c r="C802" s="2" t="inlineStr"/>
       <c r="D802" s="2" t="inlineStr"/>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>La nave espacial despega hacia la luna.</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="inlineStr">
@@ -12979,6 +15260,11 @@
       </c>
       <c r="C803" s="2" t="inlineStr"/>
       <c r="D803" s="2" t="inlineStr"/>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>En Navidad, decoramos un árbol con luces de colores.</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="inlineStr">
@@ -13025,6 +15311,11 @@
       </c>
       <c r="C806" s="2" t="inlineStr"/>
       <c r="D806" s="2" t="inlineStr"/>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Mi padre tiene un negocio de ropa.</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="inlineStr">
@@ -13043,6 +15334,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>El carbón es de color negro.</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" s="2" t="inlineStr">
@@ -13125,6 +15421,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>La niebla cubre las montañas por la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" s="2" t="inlineStr">
@@ -13143,6 +15444,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>La hija de mi hija es mi nieta.</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" s="2" t="inlineStr">
@@ -13161,6 +15467,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>El hijo de mi hijo es mi nieto.</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" s="2" t="inlineStr">
@@ -13179,6 +15490,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Los niños juegan felices en la nieve.</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" s="2" t="inlineStr">
@@ -13235,6 +15551,11 @@
       </c>
       <c r="C819" s="2" t="inlineStr"/>
       <c r="D819" s="2" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>La niña juega con sus muñecas en su habitación.</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="inlineStr">
@@ -13249,6 +15570,11 @@
       </c>
       <c r="C820" s="2" t="inlineStr"/>
       <c r="D820" s="2" t="inlineStr"/>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>El niño juega con sus juguetes en su habitación.</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="inlineStr">
@@ -13277,6 +15603,11 @@
       </c>
       <c r="C822" s="2" t="inlineStr"/>
       <c r="D822" s="2" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Salgo con mis amigos todos los sábados por la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="inlineStr">
@@ -13291,6 +15622,11 @@
       </c>
       <c r="C823" s="2" t="inlineStr"/>
       <c r="D823" s="2" t="inlineStr"/>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Mi nombre es Roberto y vivo en Londres.</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" s="2" t="inlineStr">
@@ -13319,6 +15655,11 @@
       </c>
       <c r="C825" s="2" t="inlineStr"/>
       <c r="D825" s="2" t="inlineStr"/>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Canadá está al norte de Estados Unidos.</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="inlineStr">
@@ -13397,6 +15738,11 @@
       </c>
       <c r="C830" s="2" t="inlineStr"/>
       <c r="D830" s="2" t="inlineStr"/>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Saco una nota excelente en el examen de historia.</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -13411,6 +15757,11 @@
       </c>
       <c r="C831" s="2" t="inlineStr"/>
       <c r="D831" s="2" t="inlineStr"/>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Veo las noticias en la televisión cada noche.</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -13605,6 +15956,11 @@
       </c>
       <c r="C842" s="2" t="inlineStr"/>
       <c r="D842" s="2" t="inlineStr"/>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>La mujer con la que salgo desde hace dos años es mi novia.</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="2" t="inlineStr">
@@ -13623,6 +15979,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Noviembre está entre octubre y diciembre.</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" s="2" t="inlineStr">
@@ -13637,6 +15998,11 @@
       </c>
       <c r="C844" s="2" t="inlineStr"/>
       <c r="D844" s="2" t="inlineStr"/>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>El hombre con el que salgo desde hace dos años es mi novio.</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="inlineStr">
@@ -13655,6 +16021,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Veo una nube con forma de animal en el cielo.</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="inlineStr">
@@ -13673,6 +16044,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>La esposa de mi hijo es mi nuera.</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="inlineStr">
@@ -13747,6 +16123,11 @@
       </c>
       <c r="C851" s="2" t="inlineStr"/>
       <c r="D851" s="2" t="inlineStr"/>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Marco tu número de teléfono para llamarte.</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -13789,6 +16170,11 @@
       </c>
       <c r="C854" s="2" t="inlineStr"/>
       <c r="D854" s="2" t="inlineStr"/>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Vemos una obra de teatro esta noche.</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -13803,6 +16189,11 @@
       </c>
       <c r="C855" s="2" t="inlineStr"/>
       <c r="D855" s="2" t="inlineStr"/>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Necesito obtener el permiso de mis padres para viajar.</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -14033,6 +16424,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>El otoño está en pleno apogeo en octubre.</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
@@ -14047,6 +16443,11 @@
       </c>
       <c r="C869" s="2" t="inlineStr"/>
       <c r="D869" s="2" t="inlineStr"/>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>No puedo hablar ahora, estoy muy ocupado.</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -14093,6 +16494,11 @@
       </c>
       <c r="C872" s="2" t="inlineStr"/>
       <c r="D872" s="2" t="inlineStr"/>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Siento mucho odio hacia la injusticia.</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
@@ -14107,6 +16513,11 @@
       </c>
       <c r="C873" s="2" t="inlineStr"/>
       <c r="D873" s="2" t="inlineStr"/>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>California está en la costa oeste de Estados Unidos.</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -14121,6 +16532,11 @@
       </c>
       <c r="C874" s="2" t="inlineStr"/>
       <c r="D874" s="2" t="inlineStr"/>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>La tienda tiene una oferta especial este fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="inlineStr">
@@ -14149,6 +16565,11 @@
       </c>
       <c r="C876" s="2" t="inlineStr"/>
       <c r="D876" s="2" t="inlineStr"/>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Trabajo en una oficina en el centro de la ciudad.</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="inlineStr">
@@ -14167,6 +16588,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Veo con los ojos.</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="inlineStr">
@@ -14249,6 +16675,11 @@
       </c>
       <c r="C882" s="2" t="inlineStr"/>
       <c r="D882" s="2" t="inlineStr"/>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>El cirujano realiza una operación complicada en el hospital.</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" s="2" t="inlineStr">
@@ -14263,6 +16694,11 @@
       </c>
       <c r="C883" s="2" t="inlineStr"/>
       <c r="D883" s="2" t="inlineStr"/>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Respeto tu opinión aunque no esté de acuerdo.</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="inlineStr">
@@ -14277,6 +16713,11 @@
       </c>
       <c r="C884" s="2" t="inlineStr"/>
       <c r="D884" s="2" t="inlineStr"/>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Esta es una gran oportunidad para mi carrera.</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="inlineStr">
@@ -14309,6 +16750,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Escucho con las orejas.</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" s="2" t="inlineStr">
@@ -14341,6 +16787,11 @@
       </c>
       <c r="C888" s="2" t="inlineStr"/>
       <c r="D888" s="2" t="inlineStr"/>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Los Juegos Olímpicos premian con una medalla de oro al ganador.</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
@@ -14373,6 +16824,11 @@
       </c>
       <c r="C890" s="2" t="inlineStr"/>
       <c r="D890" s="2" t="inlineStr"/>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>El cielo está oscuro porque va a llover.</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" s="2" t="inlineStr">
@@ -14391,6 +16847,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>El oso duerme todo el invierno.</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" s="2" t="inlineStr">
@@ -14423,6 +16884,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>La oveja da lana para hacer ropa.</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="2" t="inlineStr">
@@ -14455,6 +16921,11 @@
       </c>
       <c r="C895" s="2" t="inlineStr"/>
       <c r="D895" s="2" t="inlineStr"/>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>El médico examina al paciente en el hospital.</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" s="2" t="inlineStr">
@@ -14473,6 +16944,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>El hombre que me dio la vida es mi padre.</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" s="2" t="inlineStr">
@@ -14505,6 +16981,11 @@
       </c>
       <c r="C898" s="2" t="inlineStr"/>
       <c r="D898" s="2" t="inlineStr"/>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Busco el significado de esta palabra en el diccionario.</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
@@ -14523,6 +17004,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>El pan se hace con harina y agua.</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
@@ -14541,6 +17027,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Los pantalones tienen dos bolsillos delanteros.</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
@@ -14583,6 +17074,11 @@
       </c>
       <c r="C903" s="2" t="inlineStr"/>
       <c r="D903" s="2" t="inlineStr"/>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Escribo la carta en un papel blanco.</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
@@ -14675,6 +17171,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Cuelgo un cuadro en la pared.</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
@@ -14689,6 +17190,11 @@
       </c>
       <c r="C910" s="2" t="inlineStr"/>
       <c r="D910" s="2" t="inlineStr"/>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Mi pareja y yo llevamos cinco años juntos.</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -14703,6 +17209,11 @@
       </c>
       <c r="C911" s="2" t="inlineStr"/>
       <c r="D911" s="2" t="inlineStr"/>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Los niños juegan en el parque por la tarde.</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -14731,6 +17242,11 @@
       </c>
       <c r="C913" s="2" t="inlineStr"/>
       <c r="D913" s="2" t="inlineStr"/>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Vemos el partido de fútbol en la televisión.</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
@@ -14791,6 +17307,11 @@
       </c>
       <c r="C917" s="2" t="inlineStr"/>
       <c r="D917" s="2" t="inlineStr"/>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Damos un paseo por el parque después de cenar.</t>
+        </is>
+      </c>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
@@ -14823,6 +17344,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Frío patatas cortadas para hacer patatas fritas.</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
@@ -14841,6 +17367,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>El pato nada en el estanque y hace cuac.</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" s="2" t="inlineStr">
@@ -14855,6 +17386,11 @@
       </c>
       <c r="C921" s="2" t="inlineStr"/>
       <c r="D921" s="2" t="inlineStr"/>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Los dos países firman un tratado de paz.</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -14869,6 +17405,11 @@
       </c>
       <c r="C922" s="2" t="inlineStr"/>
       <c r="D922" s="2" t="inlineStr"/>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>España es un país muy bonito para visitar.</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
@@ -14887,6 +17428,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Me pongo la mano en el pecho para sentir el corazón.</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" s="2" t="inlineStr">
@@ -14937,6 +17483,11 @@
       </c>
       <c r="C926" s="2" t="inlineStr"/>
       <c r="D926" s="2" t="inlineStr"/>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Los dos hermanos tuvieron una pelea por un juguete.</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" s="2" t="inlineStr">
@@ -14969,6 +17520,11 @@
       </c>
       <c r="C928" s="2" t="inlineStr"/>
       <c r="D928" s="2" t="inlineStr"/>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Los niños están en peligro cerca del fuego.</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" s="2" t="inlineStr">
@@ -15001,6 +17557,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Me corto el pelo en la peluquería.</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" s="2" t="inlineStr">
@@ -15015,6 +17576,11 @@
       </c>
       <c r="C931" s="2" t="inlineStr"/>
       <c r="D931" s="2" t="inlineStr"/>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Vemos una película de terror esta noche.</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" s="2" t="inlineStr">
@@ -15125,6 +17691,11 @@
       </c>
       <c r="C938" s="2" t="inlineStr"/>
       <c r="D938" s="2" t="inlineStr"/>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Le pido perdón por haberle mentido.</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -15153,6 +17724,11 @@
       </c>
       <c r="C940" s="2" t="inlineStr"/>
       <c r="D940" s="2" t="inlineStr"/>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Pido permiso a mi jefe para salir temprano.</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
@@ -15203,6 +17779,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>El perro mueve la cola cuando está contento.</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" s="2" t="inlineStr">
@@ -15245,6 +17826,11 @@
       </c>
       <c r="C946" s="2" t="inlineStr"/>
       <c r="D946" s="2" t="inlineStr"/>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>A pesar de la lluvia, salimos a caminar.</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="2" t="inlineStr">
@@ -15263,6 +17849,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>El pescador saca el pescado del mar.</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" s="2" t="inlineStr">
@@ -15281,6 +17872,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Se pone rímel en las pestañas.</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="2" t="inlineStr">
@@ -15299,6 +17895,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>El pez respira por branquias.</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" s="2" t="inlineStr">
@@ -15317,6 +17918,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Los zapatos cubren los pies.</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" s="2" t="inlineStr">
@@ -15331,6 +17937,11 @@
       </c>
       <c r="C951" s="2" t="inlineStr"/>
       <c r="D951" s="2" t="inlineStr"/>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>El niño tira una piedra al lago.</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" s="2" t="inlineStr">
@@ -15349,6 +17960,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>El sol broncea la piel.</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" s="2" t="inlineStr">
@@ -15367,6 +17983,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Los pantalones cubren las piernas.</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" s="2" t="inlineStr">
@@ -15385,6 +18006,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Me pongo el pijama antes de dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" s="2" t="inlineStr">
@@ -15431,6 +18057,11 @@
       </c>
       <c r="C957" s="2" t="inlineStr"/>
       <c r="D957" s="2" t="inlineStr"/>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>El detective encuentra una pista importante para resolver el caso.</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" s="2" t="inlineStr">
@@ -15445,6 +18076,11 @@
       </c>
       <c r="C958" s="2" t="inlineStr"/>
       <c r="D958" s="2" t="inlineStr"/>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>El policía lleva una pistola en su cinturón.</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" s="2" t="inlineStr">
@@ -15473,6 +18109,11 @@
       </c>
       <c r="C960" s="2" t="inlineStr"/>
       <c r="D960" s="2" t="inlineStr"/>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Tenemos un plan para el fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" s="2" t="inlineStr">
@@ -15487,6 +18128,11 @@
       </c>
       <c r="C961" s="2" t="inlineStr"/>
       <c r="D961" s="2" t="inlineStr"/>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>La Tierra es el tercer planeta del sistema solar.</t>
+        </is>
+      </c>
     </row>
     <row r="962">
       <c r="A962" s="2" t="inlineStr">
@@ -15505,6 +18151,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>El anillo es de plata, de color plateado.</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" s="2" t="inlineStr">
@@ -15519,6 +18170,11 @@
       </c>
       <c r="C963" s="2" t="inlineStr"/>
       <c r="D963" s="2" t="inlineStr"/>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Vamos a la playa cuando hace calor.</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" s="2" t="inlineStr">
@@ -15537,6 +18193,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>El mono come un plátano amarillo.</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" s="2" t="inlineStr">
@@ -15597,6 +18258,11 @@
       </c>
       <c r="C968" s="2" t="inlineStr"/>
       <c r="D968" s="2" t="inlineStr"/>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>La policía investiga el robo en la tienda.</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" s="2" t="inlineStr">
@@ -15615,6 +18281,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Como pollo asado con arroz.</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" s="2" t="inlineStr">
@@ -15629,6 +18300,11 @@
       </c>
       <c r="C970" s="2" t="inlineStr"/>
       <c r="D970" s="2" t="inlineStr"/>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Mis padres hablan mucho de política en la cena.</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" s="2" t="inlineStr">
@@ -15679,6 +18355,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>¿Por qué llegaste tarde hoy?</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" s="2" t="inlineStr">
@@ -15707,6 +18388,11 @@
       </c>
       <c r="C975" s="2" t="inlineStr"/>
       <c r="D975" s="2" t="inlineStr"/>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Nadie entiende el porqué de su decisión.</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" s="2" t="inlineStr">
@@ -15767,6 +18453,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Pido un pastel de chocolate de postre.</t>
+        </is>
+      </c>
     </row>
     <row r="980">
       <c r="A980" s="2" t="inlineStr">
@@ -15799,6 +18490,11 @@
       </c>
       <c r="C981" s="2" t="inlineStr"/>
       <c r="D981" s="2" t="inlineStr"/>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Pregunto el precio antes de comprar el vestido.</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" s="2" t="inlineStr">
@@ -15831,6 +18527,11 @@
       </c>
       <c r="C983" s="2" t="inlineStr"/>
       <c r="D983" s="2" t="inlineStr"/>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>El profesor hace una pregunta difícil en el examen.</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" s="2" t="inlineStr">
@@ -15863,6 +18564,11 @@
       </c>
       <c r="C985" s="2" t="inlineStr"/>
       <c r="D985" s="2" t="inlineStr"/>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>La prensa informa sobre las noticias del día.</t>
+        </is>
+      </c>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
@@ -15973,6 +18679,11 @@
       </c>
       <c r="C992" s="2" t="inlineStr"/>
       <c r="D992" s="2" t="inlineStr"/>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>El presidente del país da un discurso importante.</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" s="2" t="inlineStr">
@@ -15987,6 +18698,11 @@
       </c>
       <c r="C993" s="2" t="inlineStr"/>
       <c r="D993" s="2" t="inlineStr"/>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Siento mucha presión antes del examen final.</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="2" t="inlineStr">
@@ -16009,6 +18725,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>La hija de mi tío es mi prima.</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" s="2" t="inlineStr">
@@ -16045,6 +18766,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>El hijo de mi tío es mi primo.</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" s="2" t="inlineStr">
@@ -16059,6 +18785,11 @@
       </c>
       <c r="C997" s="2" t="inlineStr"/>
       <c r="D997" s="2" t="inlineStr"/>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>La princesa vive en un castillo con el rey.</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" s="2" t="inlineStr">
@@ -16087,6 +18818,11 @@
       </c>
       <c r="C999" s="2" t="inlineStr"/>
       <c r="D999" s="2" t="inlineStr"/>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>Al principio, no entendía nada de español.</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="inlineStr">
@@ -16101,6 +18837,11 @@
       </c>
       <c r="C1000" s="2" t="inlineStr"/>
       <c r="D1000" s="2" t="inlineStr"/>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>Tengo mucha prisa porque llego tarde al trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="inlineStr">
@@ -16143,6 +18884,11 @@
       </c>
       <c r="C1003" s="2" t="inlineStr"/>
       <c r="D1003" s="2" t="inlineStr"/>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Quiero probar la comida antes de servirla.</t>
+        </is>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" s="2" t="inlineStr">
@@ -16157,6 +18903,11 @@
       </c>
       <c r="C1004" s="2" t="inlineStr"/>
       <c r="D1004" s="2" t="inlineStr"/>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Tengo un problema con mi coche esta mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="inlineStr">
@@ -16185,6 +18936,11 @@
       </c>
       <c r="C1006" s="2" t="inlineStr"/>
       <c r="D1006" s="2" t="inlineStr"/>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>El profesor enseña matemáticas en la universidad.</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="inlineStr">
@@ -16199,6 +18955,11 @@
       </c>
       <c r="C1007" s="2" t="inlineStr"/>
       <c r="D1007" s="2" t="inlineStr"/>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Veo mi programa favorito en la televisión los martes.</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="inlineStr">
@@ -16213,6 +18974,11 @@
       </c>
       <c r="C1008" s="2" t="inlineStr"/>
       <c r="D1008" s="2" t="inlineStr"/>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Quiero prometer que siempre te diré la verdad.</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="inlineStr">
@@ -16255,6 +19021,11 @@
       </c>
       <c r="C1011" s="2" t="inlineStr"/>
       <c r="D1011" s="2" t="inlineStr"/>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Lo hice a propósito, no fue un accidente.</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" s="2" t="inlineStr">
@@ -16269,6 +19040,11 @@
       </c>
       <c r="C1012" s="2" t="inlineStr"/>
       <c r="D1012" s="2" t="inlineStr"/>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Los padres quieren proteger a sus hijos del peligro.</t>
+        </is>
+      </c>
     </row>
     <row r="1013">
       <c r="A1013" s="2" t="inlineStr">
@@ -16283,6 +19059,11 @@
       </c>
       <c r="C1013" s="2" t="inlineStr"/>
       <c r="D1013" s="2" t="inlineStr"/>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Trabajamos juntos en un proyecto de la escuela.</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" s="2" t="inlineStr">
@@ -16311,6 +19092,11 @@
       </c>
       <c r="C1015" s="2" t="inlineStr"/>
       <c r="D1015" s="2" t="inlineStr"/>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>El príncipe se casa con la princesa en el castillo.</t>
+        </is>
+      </c>
     </row>
     <row r="1016">
       <c r="A1016" s="2" t="inlineStr">
@@ -16339,6 +19125,11 @@
       </c>
       <c r="C1017" s="2" t="inlineStr"/>
       <c r="D1017" s="2" t="inlineStr"/>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Mis abuelos viven en un pueblo pequeño en el campo.</t>
+        </is>
+      </c>
     </row>
     <row r="1018">
       <c r="A1018" s="2" t="inlineStr">
@@ -16353,6 +19144,11 @@
       </c>
       <c r="C1018" s="2" t="inlineStr"/>
       <c r="D1018" s="2" t="inlineStr"/>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>Cruzamos el puente para llegar a la otra orilla del río.</t>
+        </is>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" s="2" t="inlineStr">
@@ -16371,6 +19167,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Llamo a la puerta antes de entrar.</t>
+        </is>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" s="2" t="inlineStr">
@@ -16417,6 +19218,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>El aire llena el pulmón cuando respiro.</t>
+        </is>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" s="2" t="inlineStr">
@@ -16449,6 +19255,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>El pájaro construye su nido en el árbol.</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="2" t="inlineStr">
@@ -16481,6 +19292,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>En la antigua Roma, solo el emperador podía vestir de color púrpura.</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" s="2" t="inlineStr">
@@ -16595,6 +19411,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>El queso se hace con leche.</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
@@ -16659,6 +19480,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>¿Quién llamó a la puerta?</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="inlineStr">
@@ -16677,6 +19503,11 @@
           <t>questionwords</t>
         </is>
       </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>¿Qué hora es?</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="inlineStr">
@@ -16709,6 +19540,11 @@
       </c>
       <c r="C1040" s="2" t="inlineStr"/>
       <c r="D1040" s="2" t="inlineStr"/>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Escucho música en la radio mientras conduzco.</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="inlineStr">
@@ -16727,6 +19563,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>La rana salta de una hoja a otra y hace croac.</t>
+        </is>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
@@ -16773,6 +19614,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>El gato persigue al ratón.</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="inlineStr">
@@ -16787,6 +19633,11 @@
       </c>
       <c r="C1045" s="2" t="inlineStr"/>
       <c r="D1045" s="2" t="inlineStr"/>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Tienes razón, deberíamos salir más temprano.</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="inlineStr">
@@ -16815,6 +19666,11 @@
       </c>
       <c r="C1047" s="2" t="inlineStr"/>
       <c r="D1047" s="2" t="inlineStr"/>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>En realidad, no me gusta el café.</t>
+        </is>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
@@ -16879,6 +19735,11 @@
       </c>
       <c r="C1051" s="2" t="inlineStr"/>
       <c r="D1051" s="2" t="inlineStr"/>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Tengo un bonito recuerdo de mis vacaciones en la playa.</t>
+        </is>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="inlineStr">
@@ -16921,6 +19782,11 @@
       </c>
       <c r="C1054" s="2" t="inlineStr"/>
       <c r="D1054" s="2" t="inlineStr"/>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Le doy un regalo de cumpleaños a mi hermana.</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" s="2" t="inlineStr">
@@ -16967,6 +19833,11 @@
       </c>
       <c r="C1057" s="2" t="inlineStr"/>
       <c r="D1057" s="2" t="inlineStr"/>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Estoy feliz de mi regreso a casa después del viaje.</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
@@ -16981,6 +19852,11 @@
       </c>
       <c r="C1058" s="2" t="inlineStr"/>
       <c r="D1058" s="2" t="inlineStr"/>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>La reina gobierna el país junto al rey.</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
@@ -16995,6 +19871,11 @@
       </c>
       <c r="C1059" s="2" t="inlineStr"/>
       <c r="D1059" s="2" t="inlineStr"/>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>Tenemos una relación muy fuerte desde hace años.</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
@@ -17009,6 +19890,11 @@
       </c>
       <c r="C1060" s="2" t="inlineStr"/>
       <c r="D1060" s="2" t="inlineStr"/>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Miro el reloj para saber qué hora es.</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
@@ -17027,6 +19913,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>El relámpago ilumina el cielo justo antes de oír el trueno.</t>
+        </is>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
@@ -17041,6 +19932,11 @@
       </c>
       <c r="C1062" s="2" t="inlineStr"/>
       <c r="D1062" s="2" t="inlineStr"/>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>De repente, empezó a llover muy fuerte.</t>
+        </is>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
@@ -17055,6 +19951,11 @@
       </c>
       <c r="C1063" s="2" t="inlineStr"/>
       <c r="D1063" s="2" t="inlineStr"/>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>Con respecto a tu pregunta, no tengo la respuesta.</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
@@ -17069,6 +19970,11 @@
       </c>
       <c r="C1064" s="2" t="inlineStr"/>
       <c r="D1064" s="2" t="inlineStr"/>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>Trato a mis mayores con mucho respeto.</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
@@ -17101,6 +20007,11 @@
       </c>
       <c r="C1066" s="2" t="inlineStr"/>
       <c r="D1066" s="2" t="inlineStr"/>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>El conductor es responsable del accidente.</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
@@ -17115,6 +20026,11 @@
       </c>
       <c r="C1067" s="2" t="inlineStr"/>
       <c r="D1067" s="2" t="inlineStr"/>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Espero tu respuesta a mi pregunta.</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
@@ -17129,6 +20045,11 @@
       </c>
       <c r="C1068" s="2" t="inlineStr"/>
       <c r="D1068" s="2" t="inlineStr"/>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>Cenamos en un restaurante italiano anoche.</t>
+        </is>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
@@ -17171,6 +20092,11 @@
       </c>
       <c r="C1071" s="2" t="inlineStr"/>
       <c r="D1071" s="2" t="inlineStr"/>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>Tenemos una reunión de trabajo a las diez.</t>
+        </is>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
@@ -17185,6 +20111,11 @@
       </c>
       <c r="C1072" s="2" t="inlineStr"/>
       <c r="D1072" s="2" t="inlineStr"/>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>El rey vive en un palacio con la reina.</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
@@ -17245,6 +20176,11 @@
       </c>
       <c r="C1076" s="2" t="inlineStr"/>
       <c r="D1076" s="2" t="inlineStr"/>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Es un gran riesgo conducir sin cinturón de seguridad.</t>
+        </is>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
@@ -17259,6 +20195,11 @@
       </c>
       <c r="C1077" s="2" t="inlineStr"/>
       <c r="D1077" s="2" t="inlineStr"/>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>El ladrón intenta robar el banco.</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" s="2" t="inlineStr">
@@ -17273,6 +20214,11 @@
       </c>
       <c r="C1078" s="2" t="inlineStr"/>
       <c r="D1078" s="2" t="inlineStr"/>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>La policía investiga el robo del banco.</t>
+        </is>
+      </c>
     </row>
     <row r="1079">
       <c r="A1079" s="2" t="inlineStr">
@@ -17291,6 +20237,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>Los pantalones tienen un agujero en la rodilla.</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" s="2" t="inlineStr">
@@ -17309,6 +20260,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>El tomate maduro es de color rojo.</t>
+        </is>
+      </c>
     </row>
     <row r="1081">
       <c r="A1081" s="2" t="inlineStr">
@@ -17341,6 +20297,11 @@
       </c>
       <c r="C1082" s="2" t="inlineStr"/>
       <c r="D1082" s="2" t="inlineStr"/>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Compro ropa nueva para el verano.</t>
+        </is>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="inlineStr">
@@ -17359,6 +20320,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>La ropa interior se lleva debajo de la demás ropa.</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
@@ -17377,6 +20343,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>La flor llamada rosa le da su nombre a este color.</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
@@ -17405,6 +20376,11 @@
       </c>
       <c r="C1086" s="2" t="inlineStr"/>
       <c r="D1086" s="2" t="inlineStr"/>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>No puedo dormir por el ruido de la calle.</t>
+        </is>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
@@ -17419,6 +20395,11 @@
       </c>
       <c r="C1087" s="2" t="inlineStr"/>
       <c r="D1087" s="2" t="inlineStr"/>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>El guepardo es el animal más rápido del mundo.</t>
+        </is>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
@@ -17433,6 +20414,11 @@
       </c>
       <c r="C1088" s="2" t="inlineStr"/>
       <c r="D1088" s="2" t="inlineStr"/>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Pescamos peces en el río cerca de casa.</t>
+        </is>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
@@ -17491,6 +20477,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Pongo sal en la comida porque está sosa.</t>
+        </is>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" s="2" t="inlineStr">
@@ -17509,6 +20500,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Vemos la televisión juntos en la sala.</t>
+        </is>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" s="2" t="inlineStr">
@@ -17523,6 +20519,11 @@
       </c>
       <c r="C1093" s="2" t="inlineStr"/>
       <c r="D1093" s="2" t="inlineStr"/>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Busco la salida de emergencia del edificio.</t>
+        </is>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="inlineStr">
@@ -17573,6 +20574,11 @@
       </c>
       <c r="C1096" s="2" t="inlineStr"/>
       <c r="D1096" s="2" t="inlineStr"/>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Como verduras para cuidar mi salud.</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="inlineStr">
@@ -17623,6 +20629,11 @@
       </c>
       <c r="C1099" s="2" t="inlineStr"/>
       <c r="D1099" s="2" t="inlineStr"/>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>El bombero arriesga su vida para salvar al niño.</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" s="2" t="inlineStr">
@@ -17669,6 +20680,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Me pongo las sandalias en la playa porque hace calor.</t>
+        </is>
+      </c>
     </row>
     <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
@@ -17683,6 +20699,11 @@
       </c>
       <c r="C1103" s="2" t="inlineStr"/>
       <c r="D1103" s="2" t="inlineStr"/>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>El médico saca sangre para hacer un análisis.</t>
+        </is>
+      </c>
     </row>
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
@@ -17711,6 +20732,11 @@
       </c>
       <c r="C1105" s="2" t="inlineStr"/>
       <c r="D1105" s="2" t="inlineStr"/>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>El sargento da órdenes a los soldados nuevos.</t>
+        </is>
+      </c>
     </row>
     <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
@@ -17725,6 +20751,11 @@
       </c>
       <c r="C1106" s="2" t="inlineStr"/>
       <c r="D1106" s="2" t="inlineStr"/>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>No le cuento mi secreto a nadie.</t>
+        </is>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
@@ -17785,6 +20816,11 @@
       </c>
       <c r="C1110" s="2" t="inlineStr"/>
       <c r="D1110" s="2" t="inlineStr"/>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>El guardia de seguridad vigila el edificio toda la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" s="2" t="inlineStr">
@@ -17845,6 +20881,11 @@
       </c>
       <c r="C1114" s="2" t="inlineStr"/>
       <c r="D1114" s="2" t="inlineStr"/>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Trabajo cinco días a la semana.</t>
+        </is>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" s="2" t="inlineStr">
@@ -17941,6 +20982,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Las clases empiezan en septiembre.</t>
+        </is>
+      </c>
     </row>
     <row r="1121">
       <c r="A1121" s="2" t="inlineStr">
@@ -17977,6 +21023,11 @@
       </c>
       <c r="C1122" s="2" t="inlineStr"/>
       <c r="D1122" s="2" t="inlineStr"/>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Veo una serie nueva en la televisión cada noche.</t>
+        </is>
+      </c>
     </row>
     <row r="1123">
       <c r="A1123" s="2" t="inlineStr">
@@ -18009,6 +21060,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>La serpiente no tiene patas y se desliza por el suelo.</t>
+        </is>
+      </c>
     </row>
     <row r="1125">
       <c r="A1125" s="2" t="inlineStr">
@@ -18023,6 +21079,11 @@
       </c>
       <c r="C1125" s="2" t="inlineStr"/>
       <c r="D1125" s="2" t="inlineStr"/>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>El restaurante tiene un servicio muy rápido.</t>
+        </is>
+      </c>
     </row>
     <row r="1126">
       <c r="A1126" s="2" t="inlineStr">
@@ -18037,6 +21098,11 @@
       </c>
       <c r="C1126" s="2" t="inlineStr"/>
       <c r="D1126" s="2" t="inlineStr"/>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>El camarero va a servir la comida pronto.</t>
+        </is>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" s="2" t="inlineStr">
@@ -18411,6 +21477,11 @@
       </c>
       <c r="C1147" s="2" t="inlineStr"/>
       <c r="D1147" s="2" t="inlineStr"/>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>El conductor no vio la señal de stop.</t>
+        </is>
+      </c>
     </row>
     <row r="1148">
       <c r="A1148" s="2" t="inlineStr">
@@ -18555,6 +21626,11 @@
       </c>
       <c r="C1157" s="2" t="inlineStr"/>
       <c r="D1157" s="2" t="inlineStr"/>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Pido silencio en la biblioteca porque hay mucha gente estudiando.</t>
+        </is>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" s="2" t="inlineStr">
@@ -18573,6 +21649,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Me siento en la silla para descansar las piernas.</t>
+        </is>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" s="2" t="inlineStr">
@@ -18717,6 +21798,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>La hija de mi hermano es mi sobrina.</t>
+        </is>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" s="2" t="inlineStr">
@@ -18735,6 +21821,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>El hijo de mi hermano es mi sobrino.</t>
+        </is>
+      </c>
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="inlineStr">
@@ -18767,6 +21858,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Nos sentamos en el sofá para ver una película.</t>
+        </is>
+      </c>
     </row>
     <row r="1172">
       <c r="A1172" s="2" t="inlineStr">
@@ -18785,6 +21881,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>El sol sale por la mañana y se pone por la noche.</t>
+        </is>
+      </c>
     </row>
     <row r="1173">
       <c r="A1173" s="2" t="inlineStr">
@@ -18813,6 +21914,11 @@
       </c>
       <c r="C1174" s="2" t="inlineStr"/>
       <c r="D1174" s="2" t="inlineStr"/>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>El soldado lucha por defender su país.</t>
+        </is>
+      </c>
     </row>
     <row r="1175">
       <c r="A1175" s="2" t="inlineStr">
@@ -18863,6 +21969,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Me pongo el sombrero para protegerme del sol.</t>
+        </is>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" s="2" t="inlineStr">
@@ -18891,6 +22002,11 @@
       </c>
       <c r="C1179" s="2" t="inlineStr"/>
       <c r="D1179" s="2" t="inlineStr"/>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>El sonido de la lluvia me ayuda a dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="1180">
       <c r="A1180" s="2" t="inlineStr">
@@ -18927,6 +22043,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Como sopa caliente cuando estoy resfriado.</t>
+        </is>
+      </c>
     </row>
     <row r="1182">
       <c r="A1182" s="2" t="inlineStr">
@@ -18959,6 +22080,11 @@
       </c>
       <c r="C1183" s="2" t="inlineStr"/>
       <c r="D1183" s="2" t="inlineStr"/>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Le doy una sorpresa a mi madre el día de su cumpleaños.</t>
+        </is>
+      </c>
     </row>
     <row r="1184">
       <c r="A1184" s="2" t="inlineStr">
@@ -18973,6 +22099,11 @@
       </c>
       <c r="C1184" s="2" t="inlineStr"/>
       <c r="D1184" s="2" t="inlineStr"/>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>La policía interroga al sospechoso del robo.</t>
+        </is>
+      </c>
     </row>
     <row r="1185">
       <c r="A1185" s="2" t="inlineStr">
@@ -19037,6 +22168,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>La madre de mi esposo es mi suegra.</t>
+        </is>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" s="2" t="inlineStr">
@@ -19055,6 +22191,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>El padre de mi esposo es mi suegro.</t>
+        </is>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" s="2" t="inlineStr">
@@ -19073,6 +22214,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Se me cayó el vaso y se rompió contra el suelo.</t>
+        </is>
+      </c>
     </row>
     <row r="1191">
       <c r="A1191" s="2" t="inlineStr">
@@ -19087,6 +22233,11 @@
       </c>
       <c r="C1191" s="2" t="inlineStr"/>
       <c r="D1191" s="2" t="inlineStr"/>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Tengo mucha suerte de tener una familia tan buena.</t>
+        </is>
+      </c>
     </row>
     <row r="1192">
       <c r="A1192" s="2" t="inlineStr">
@@ -19101,6 +22252,11 @@
       </c>
       <c r="C1192" s="2" t="inlineStr"/>
       <c r="D1192" s="2" t="inlineStr"/>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Anoche tuve un sueño extraño sobre volar.</t>
+        </is>
+      </c>
     </row>
     <row r="1193">
       <c r="A1193" s="2" t="inlineStr">
@@ -19157,6 +22313,11 @@
       </c>
       <c r="C1196" s="2" t="inlineStr"/>
       <c r="D1196" s="2" t="inlineStr"/>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Argentina está en el sur de Sudamérica.</t>
+        </is>
+      </c>
     </row>
     <row r="1197">
       <c r="A1197" s="2" t="inlineStr">
@@ -19189,6 +22350,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Me pongo un suéter de lana cuando hace frío.</t>
+        </is>
+      </c>
     </row>
     <row r="1199">
       <c r="A1199" s="2" t="inlineStr">
@@ -19207,6 +22373,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>El sábado es el primer día del fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="1200">
       <c r="A1200" s="2" t="inlineStr">
@@ -19253,6 +22424,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>El zapato me aprieta en el talón.</t>
+        </is>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" s="2" t="inlineStr">
@@ -19337,6 +22513,11 @@
       </c>
       <c r="C1208" s="2" t="inlineStr"/>
       <c r="D1208" s="2" t="inlineStr"/>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Pago con tarjeta de crédito en la tienda.</t>
+        </is>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" s="2" t="inlineStr">
@@ -19355,6 +22536,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Levanto la mano para parar un taxi en la calle.</t>
+        </is>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" s="2" t="inlineStr">
@@ -19373,6 +22559,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Las goteras entran por el techo cuando llueve.</t>
+        </is>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" s="2" t="inlineStr">
@@ -19387,6 +22578,11 @@
       </c>
       <c r="C1211" s="2" t="inlineStr"/>
       <c r="D1211" s="2" t="inlineStr"/>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Vemos la televisión juntos después de cenar.</t>
+        </is>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" s="2" t="inlineStr">
@@ -19405,6 +22601,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Encendemos el televisor para ver las noticias.</t>
+        </is>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" s="2" t="inlineStr">
@@ -19419,6 +22620,11 @@
       </c>
       <c r="C1213" s="2" t="inlineStr"/>
       <c r="D1213" s="2" t="inlineStr"/>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Hablo por teléfono con mi madre todos los días.</t>
+        </is>
+      </c>
     </row>
     <row r="1214">
       <c r="A1214" s="2" t="inlineStr">
@@ -19433,6 +22639,11 @@
       </c>
       <c r="C1214" s="2" t="inlineStr"/>
       <c r="D1214" s="2" t="inlineStr"/>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>El profesor explica un tema difícil en la clase.</t>
+        </is>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" s="2" t="inlineStr">
@@ -19461,6 +22672,11 @@
       </c>
       <c r="C1216" s="2" t="inlineStr"/>
       <c r="D1216" s="2" t="inlineStr"/>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Me levanto temprano para ir al trabajo.</t>
+        </is>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" s="2" t="inlineStr">
@@ -19479,6 +22695,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>No puedo tener mascotas en mi apartamento.</t>
+        </is>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" s="2" t="inlineStr">
@@ -19493,6 +22714,11 @@
       </c>
       <c r="C1218" s="2" t="inlineStr"/>
       <c r="D1218" s="2" t="inlineStr"/>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>El teniente recibe órdenes del capitán.</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" s="2" t="inlineStr">
@@ -19539,6 +22765,11 @@
       </c>
       <c r="C1221" s="2" t="inlineStr"/>
       <c r="D1221" s="2" t="inlineStr"/>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>El testigo describe lo que vio en el juicio.</t>
+        </is>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" s="2" t="inlineStr">
@@ -19571,6 +22802,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>El tiburón tiene muchos dientes afilados.</t>
+        </is>
+      </c>
     </row>
     <row r="1224">
       <c r="A1224" s="2" t="inlineStr">
@@ -19599,6 +22835,11 @@
       </c>
       <c r="C1225" s="2" t="inlineStr"/>
       <c r="D1225" s="2" t="inlineStr"/>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Compro ropa nueva en la tienda del centro comercial.</t>
+        </is>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" s="2" t="inlineStr">
@@ -19613,6 +22854,11 @@
       </c>
       <c r="C1226" s="2" t="inlineStr"/>
       <c r="D1226" s="2" t="inlineStr"/>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Las plantas crecen en la tierra fértil.</t>
+        </is>
+      </c>
     </row>
     <row r="1227">
       <c r="A1227" s="2" t="inlineStr">
@@ -19631,6 +22877,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>El tigre tiene rayas negras y naranjas.</t>
+        </is>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" s="2" t="inlineStr">
@@ -19695,6 +22946,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Me torcí el tobillo jugando fútbol.</t>
+        </is>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" s="2" t="inlineStr">
@@ -19777,6 +23033,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Corto el tomate para hacer la ensalada.</t>
+        </is>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" s="2" t="inlineStr">
@@ -19823,6 +23084,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Durante la tormenta, el cielo se llena de relámpagos y truenos.</t>
+        </is>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" s="2" t="inlineStr">
@@ -19841,6 +23107,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>La tortuga camina muy despacio pero vive muchos años.</t>
+        </is>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" s="2" t="inlineStr">
@@ -19887,6 +23158,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Necesito trabajar duro para ganar dinero.</t>
+        </is>
+      </c>
     </row>
     <row r="1244">
       <c r="A1244" s="2" t="inlineStr">
@@ -19901,6 +23177,11 @@
       </c>
       <c r="C1244" s="2" t="inlineStr"/>
       <c r="D1244" s="2" t="inlineStr"/>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Voy al trabajo en autobús todos los días.</t>
+        </is>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" s="2" t="inlineStr">
@@ -19951,6 +23232,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Me pongo un traje para ir a la boda de mi hermano.</t>
+        </is>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" s="2" t="inlineStr">
@@ -19965,6 +23251,11 @@
       </c>
       <c r="C1248" s="2" t="inlineStr"/>
       <c r="D1248" s="2" t="inlineStr"/>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>El cazador pone una trampa para atrapar al animal.</t>
+        </is>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" s="2" t="inlineStr">
@@ -20001,6 +23292,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>El tranvía circula sobre raíles por el centro de la ciudad.</t>
+        </is>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" s="2" t="inlineStr">
@@ -20075,6 +23371,11 @@
       </c>
       <c r="C1255" s="2" t="inlineStr"/>
       <c r="D1255" s="2" t="inlineStr"/>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Me comunico con mi familia a través de videollamadas.</t>
+        </is>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" s="2" t="inlineStr">
@@ -20291,6 +23592,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>El tren llega a la estación circulando sobre las vías.</t>
+        </is>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" s="2" t="inlineStr">
@@ -20345,6 +23651,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Después de ver el relámpago, se escucha el trueno.</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" s="2" t="inlineStr">
@@ -20373,6 +23684,11 @@
       </c>
       <c r="C1272" s="2" t="inlineStr"/>
       <c r="D1272" s="2" t="inlineStr"/>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Espero mi turno en la fila del banco.</t>
+        </is>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" s="2" t="inlineStr">
@@ -20391,6 +23707,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>El mar Caribe tiene un color turquesa muy famoso.</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" s="2" t="inlineStr">
@@ -20423,6 +23744,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Pongo una bolsita en agua caliente para hacer té.</t>
+        </is>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" s="2" t="inlineStr">
@@ -20441,6 +23767,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>La hermana de mi madre es mi tía.</t>
+        </is>
+      </c>
     </row>
     <row r="1277">
       <c r="A1277" s="2" t="inlineStr">
@@ -20459,6 +23790,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>El hermano de mi madre es mi tío.</t>
+        </is>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" s="2" t="inlineStr">
@@ -20519,6 +23855,11 @@
       </c>
       <c r="C1281" s="2" t="inlineStr"/>
       <c r="D1281" s="2" t="inlineStr"/>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Estudio ingeniería en la universidad.</t>
+        </is>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" s="2" t="inlineStr">
@@ -20533,6 +23874,11 @@
       </c>
       <c r="C1282" s="2" t="inlineStr"/>
       <c r="D1282" s="2" t="inlineStr"/>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Los científicos estudian el origen del universo.</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" s="2" t="inlineStr">
@@ -20619,6 +23965,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>El vino se hace con uva.</t>
+        </is>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" s="2" t="inlineStr">
@@ -20637,6 +23988,11 @@
           <t>bodyparts</t>
         </is>
       </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Se pinta las uñas de color rosa.</t>
+        </is>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" s="2" t="inlineStr">
@@ -20655,6 +24011,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>La vaca da leche todos los días.</t>
+        </is>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" s="2" t="inlineStr">
@@ -20669,6 +24030,11 @@
       </c>
       <c r="C1290" s="2" t="inlineStr"/>
       <c r="D1290" s="2" t="inlineStr"/>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Vamos de vacaciones a la playa en verano.</t>
+        </is>
+      </c>
     </row>
     <row r="1291">
       <c r="A1291" s="2" t="inlineStr">
@@ -20891,6 +24257,11 @@
       </c>
       <c r="C1303" s="2" t="inlineStr"/>
       <c r="D1303" s="2" t="inlineStr"/>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>El coche conduce a mucha velocidad por la autopista.</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" s="2" t="inlineStr">
@@ -20945,6 +24316,11 @@
           <t>house</t>
         </is>
       </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Miro el jardín a través de la ventana.</t>
+        </is>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" s="2" t="inlineStr">
@@ -20963,6 +24339,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Me gusta ver películas los fines de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" s="2" t="inlineStr">
@@ -20977,6 +24358,11 @@
       </c>
       <c r="C1308" s="2" t="inlineStr"/>
       <c r="D1308" s="2" t="inlineStr"/>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Vamos a la playa todos los veranos.</t>
+        </is>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" s="2" t="inlineStr">
@@ -20991,6 +24377,11 @@
       </c>
       <c r="C1309" s="2" t="inlineStr"/>
       <c r="D1309" s="2" t="inlineStr"/>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Siempre digo la verdad a mis amigos.</t>
+        </is>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" s="2" t="inlineStr">
@@ -21023,6 +24414,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>La hierba fresca es de color verde.</t>
+        </is>
+      </c>
     </row>
     <row r="1312">
       <c r="A1312" s="2" t="inlineStr">
@@ -21041,6 +24437,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>El brócoli y la zanahoria son mis verduras favoritas.</t>
+        </is>
+      </c>
     </row>
     <row r="1313">
       <c r="A1313" s="2" t="inlineStr">
@@ -21055,6 +24456,11 @@
       </c>
       <c r="C1313" s="2" t="inlineStr"/>
       <c r="D1313" s="2" t="inlineStr"/>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Siento mucha vergüenza cuando hablo en público.</t>
+        </is>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" s="2" t="inlineStr">
@@ -21073,6 +24479,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Ella lleva un vestido sin mangas.</t>
+        </is>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" s="2" t="inlineStr">
@@ -21091,6 +24502,11 @@
           <t>conjugation,dailyverbs</t>
         </is>
       </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Los niños tardan mucho en vestirse por las mañanas.</t>
+        </is>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" s="2" t="inlineStr">
@@ -21137,6 +24553,11 @@
       </c>
       <c r="C1318" s="2" t="inlineStr"/>
       <c r="D1318" s="2" t="inlineStr"/>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Hacemos un viaje a Europa este verano.</t>
+        </is>
+      </c>
     </row>
     <row r="1319">
       <c r="A1319" s="2" t="inlineStr">
@@ -21151,6 +24572,11 @@
       </c>
       <c r="C1319" s="2" t="inlineStr"/>
       <c r="D1319" s="2" t="inlineStr"/>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Disfruto cada momento de mi vida.</t>
+        </is>
+      </c>
     </row>
     <row r="1320">
       <c r="A1320" s="2" t="inlineStr">
@@ -21183,6 +24609,11 @@
           <t>weather</t>
         </is>
       </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Vuelo la cometa cuando hay mucho viento.</t>
+        </is>
+      </c>
     </row>
     <row r="1322">
       <c r="A1322" s="2" t="inlineStr">
@@ -21201,6 +24632,11 @@
           <t>daysandmonths</t>
         </is>
       </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Los estudiantes esperan el viernes porque empieza el fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" s="2" t="inlineStr">
@@ -21219,6 +24655,11 @@
           <t>foodanddrink</t>
         </is>
       </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Brindamos con una copa de vino en la boda.</t>
+        </is>
+      </c>
     </row>
     <row r="1324">
       <c r="A1324" s="2" t="inlineStr">
@@ -21237,6 +24678,11 @@
           <t>colours</t>
         </is>
       </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Las violetas son flores pequeñas de color violeta.</t>
+        </is>
+      </c>
     </row>
     <row r="1325">
       <c r="A1325" s="2" t="inlineStr">
@@ -21251,6 +24697,11 @@
       </c>
       <c r="C1325" s="2" t="inlineStr"/>
       <c r="D1325" s="2" t="inlineStr"/>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Recibimos la visita de mis abuelos este fin de semana.</t>
+        </is>
+      </c>
     </row>
     <row r="1326">
       <c r="A1326" s="2" t="inlineStr">
@@ -21397,6 +24848,11 @@
       </c>
       <c r="C1334" s="2" t="inlineStr"/>
       <c r="D1334" s="2" t="inlineStr"/>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Canto con una voz muy fuerte en el karaoke.</t>
+        </is>
+      </c>
     </row>
     <row r="1335">
       <c r="A1335" s="2" t="inlineStr">
@@ -21411,6 +24867,11 @@
       </c>
       <c r="C1335" s="2" t="inlineStr"/>
       <c r="D1335" s="2" t="inlineStr"/>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Nuestro vuelo sale a las ocho de la mañana.</t>
+        </is>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" s="2" t="inlineStr">
@@ -21457,6 +24918,11 @@
       </c>
       <c r="C1338" s="2" t="inlineStr"/>
       <c r="D1338" s="2" t="inlineStr"/>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>La víctima del accidente está en el hospital.</t>
+        </is>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" s="2" t="inlineStr">
@@ -21503,6 +24969,11 @@
           <t>family</t>
         </is>
       </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>El esposo de mi hija es mi yerno.</t>
+        </is>
+      </c>
     </row>
     <row r="1342">
       <c r="A1342" s="2" t="inlineStr">
@@ -21549,6 +25020,11 @@
           <t>clothing</t>
         </is>
       </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Antes de entrar en casa, me quito los zapatos.</t>
+        </is>
+      </c>
     </row>
     <row r="1345">
       <c r="A1345" s="2" t="inlineStr">
@@ -21581,6 +25057,11 @@
           <t>animals</t>
         </is>
       </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>El zorro es tan astuto como dice el dicho.</t>
+        </is>
+      </c>
     </row>
     <row r="1347">
       <c r="A1347" s="2" t="inlineStr">
@@ -21595,6 +25076,11 @@
       </c>
       <c r="C1347" s="2" t="inlineStr"/>
       <c r="D1347" s="2" t="inlineStr"/>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Dicen que un ángel te protege desde el cielo.</t>
+        </is>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" s="2" t="inlineStr">
@@ -21609,6 +25095,11 @@
       </c>
       <c r="C1348" s="2" t="inlineStr"/>
       <c r="D1348" s="2" t="inlineStr"/>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>En otoño, las hojas del árbol se caen.</t>
+        </is>
+      </c>
     </row>
     <row r="1349">
       <c r="A1349" s="2" t="inlineStr">
@@ -21651,6 +25142,11 @@
       </c>
       <c r="C1351" s="2" t="inlineStr"/>
       <c r="D1351" s="2" t="inlineStr"/>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Vivimos en una época de mucha tecnología.</t>
+        </is>
+      </c>
     </row>
     <row r="1352">
       <c r="A1352" s="2" t="inlineStr">
@@ -21665,6 +25161,11 @@
       </c>
       <c r="C1352" s="2" t="inlineStr"/>
       <c r="D1352" s="2" t="inlineStr"/>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>La película tuvo mucho éxito en el cine.</t>
+        </is>
+      </c>
     </row>
     <row r="1353">
       <c r="A1353" s="2" t="inlineStr">
